--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00 &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,8 +78,67 @@
       <color rgb="000284C7"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -110,8 +169,20 @@
         <bgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -202,11 +273,53 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -287,6 +400,93 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -667,14 +867,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>ИНВЕСТИЦИОННАЯ СВОДКА И ДАШБОРД ПРОЕКТА</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Флиппинг 2-комн. квартиры: г. Тула, ул. Фрунзе 17, кв. 76 (43.2 м²)</t>
         </is>
@@ -721,226 +921,226 @@
       <c r="H5" s="24" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
         <is>
           <t>ФИНАНСОВЫЙ БАЛАНС И СРАВНЕНИЕ С РЫНКОМ</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>Статья бюджета / Показатель</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>Рыночный ориентир (₽)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="42" t="inlineStr">
         <is>
           <t>Наш план / Факт (₽)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>Экономия за счёт оптимизации (₽)</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="43" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t>1. Стоимость покупки квартиры</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="45" t="n">
         <v>3900000</v>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="46" t="n">
         <v>3900000</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="47">
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="48" t="inlineStr">
         <is>
           <t>Оплачено</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>2. Начальные расходы (ЭЦП, госпошлина, вскрытие)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="50" t="n">
         <v>20000</v>
       </c>
-      <c r="C12" s="10">
-        <f>'Факт расходов'!F18</f>
-        <v/>
-      </c>
-      <c r="D12" s="10">
+      <c r="C12" s="51">
+        <f>'Факт расходов'!F22</f>
+        <v/>
+      </c>
+      <c r="D12" s="47">
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="52" t="inlineStr">
         <is>
           <t>Оплачено</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>3. Смета ремонта и чистовой отделки</t>
         </is>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="45">
         <f>'План vs Рынок (Смета)'!D16</f>
         <v/>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="46">
         <f>'План vs Рынок (Смета)'!E16</f>
         <v/>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="47">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="53" t="inlineStr">
         <is>
           <t>В процессе</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>4. Экономия на окнах ПВХ (сохранены)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="50" t="n">
         <v>120000</v>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="47" t="n">
         <v>120000</v>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="52" t="inlineStr">
         <is>
           <t>Сэкономлено</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>5. Экономия на стояке канализации (сохранен)</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="45" t="n">
         <v>15000</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="47" t="n">
         <v>15000</v>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="48" t="inlineStr">
         <is>
           <t>Сэкономлено</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>6. Экономия на счётчике СОЛО (пломба 02.2024)</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="50" t="n">
         <v>7000</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="47" t="n">
         <v>7000</v>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="52" t="inlineStr">
         <is>
           <t>Сэкономлено</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>ВСЕГО ЗАТРАТ НА ПРОЕКТ (ПОКУПКА + РЕМОНТ):</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="55">
         <f>B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="55">
         <f>C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="56">
         <f>D11+D12+D13+D14+D15+D16</f>
         <v/>
       </c>
-      <c r="E18" s="14" t="n"/>
-    </row>
-    <row r="20">
+      <c r="E18" s="57" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Выручка от продажи (таргет):</t>
         </is>
       </c>
       <c r="B20" s="4" t="n"/>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="58" t="n">
         <v>5600000</v>
       </c>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>ЧИСТАЯ ПРИБЫЛЬ ИНВЕСТОРА:</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
-      <c r="C21" s="16">
+      <c r="C21" s="60">
         <f>C20-C18</f>
         <v/>
       </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="22" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Рентабельность инвестиций (ROI на цикл):</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
-      <c r="C22" s="17">
+      <c r="C22" s="61">
         <f>C21/C18</f>
         <v/>
       </c>
@@ -964,7 +1164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="71" customWidth="1" min="1" max="1"/>
@@ -980,110 +1180,110 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>ЖУРНАЛ ФАКТИЧЕСКИХ РАСХОДОВ — ФРУНЗЕ 17</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Объект: г. Тула, ул. Фрунзе 17, кв. 76 (2-комн., 43.2 м²) | Флиппинг</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>Наименование расхода / Работы</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>Рыночная цена (₽)</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>Факт оплачено (₽)</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>Экономия (₽)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="43" t="inlineStr">
         <is>
           <t>% Экономии</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>Исполнитель / Поставщик</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="41" t="inlineStr">
         <is>
           <t>Примечание / Чек</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="n">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>18.08.2026</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Юр. оформление / Торги</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>Выпуск ЭЦП (электронная цифровая подпись)</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="45" t="n">
         <v>7000</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="46" t="n">
         <v>7000</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="47">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="63">
         <f>IFERROR(G5/E5, 0)</f>
         <v/>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>УЦ / Контур</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>Для участия в торгах и регистрации</t>
         </is>
@@ -1093,45 +1293,45 @@
       <c r="M5" s="30" t="n"/>
       <c r="N5" s="30" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="n">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>18.08.2026</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>Юр. оформление / Торги</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="49" t="inlineStr">
         <is>
           <t>Государственная пошлина (регистрация права)</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="50" t="n">
         <v>5000</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="51" t="n">
         <v>5000</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="47">
         <f>E6-F6</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="63">
         <f>IFERROR(G6/E6, 0)</f>
         <v/>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="49" t="inlineStr">
         <is>
           <t>Росреестр</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="49" t="inlineStr">
         <is>
           <t>Госпошлина за переход права</t>
         </is>
@@ -1141,45 +1341,45 @@
       <c r="M6" s="30" t="n"/>
       <c r="N6" s="30" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="62" t="inlineStr">
         <is>
           <t>18.08.2026</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
         <is>
           <t>Безопасность / Доступ</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="44" t="inlineStr">
         <is>
           <t>Вскрытие старого замка и обеспечение доступа</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="45" t="n">
         <v>8000</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="46" t="n">
         <v>8000</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="47">
         <f>E7-F7</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="63">
         <f>IFERROR(G7/E7, 0)</f>
         <v/>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="44" t="inlineStr">
         <is>
           <t>Служба вскрытия</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="44" t="inlineStr">
         <is>
           <t>Аварийное открытие входной двери объекта</t>
         </is>
@@ -1189,45 +1389,45 @@
       <c r="M7" s="30" t="n"/>
       <c r="N7" s="30" t="n"/>
     </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="64" t="inlineStr">
         <is>
           <t>22.08.2026</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>Демонтаж и зачистка</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="49" t="inlineStr">
         <is>
           <t>Заказ мусорного контейнера 8 м³</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="50" t="n">
         <v>9000</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="51" t="n">
         <v>8500</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="47">
         <f>E8-F8</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="63">
         <f>IFERROR(G8/E8, 0)</f>
         <v/>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>Елена (контейнер)</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="I8" s="49" t="inlineStr">
+        <is>
+          <t>Елена (вывоз мусора)</t>
+        </is>
+      </c>
+      <c r="J8" s="49" t="inlineStr">
         <is>
           <t>Вывоз мебели, санузла, чугуна и строительного боя (скидка 500 ₽)</t>
         </is>
@@ -1237,45 +1437,45 @@
       <c r="M8" s="30" t="n"/>
       <c r="N8" s="30" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="62" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="62" t="inlineStr">
         <is>
           <t>22.08.2026</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="44" t="inlineStr">
         <is>
           <t>Демонтаж и зачистка</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="44" t="inlineStr">
         <is>
           <t>Аренда/помощь инструментом соседа</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="46" t="n">
         <v>1000</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="47">
         <f>E9-F9</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="63">
         <f>IFERROR(G9/E9, 0)</f>
         <v/>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="44" t="inlineStr">
         <is>
           <t>Сосед по дому</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="44" t="inlineStr">
         <is>
           <t>Перфоратор/монтировки/инструмент (экономия 1 500 ₽)</t>
         </is>
@@ -1285,45 +1485,45 @@
       <c r="M9" s="30" t="n"/>
       <c r="N9" s="30" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="64" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="64" t="inlineStr">
         <is>
           <t>22.08.2026</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>Расходные материалы</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="49" t="inlineStr">
         <is>
           <t>Мешки мусорные плотные, перчатки рабочие</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="50" t="n">
         <v>500</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="51" t="n">
         <v>300</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="47">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="63">
         <f>IFERROR(G10/E10, 0)</f>
         <v/>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="49" t="inlineStr">
         <is>
           <t>Хозмаг / Рынок</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="49" t="inlineStr">
         <is>
           <t>Расходники для сбора и выноса строительного мусора</t>
         </is>
@@ -1333,45 +1533,45 @@
       <c r="M10" s="30" t="n"/>
       <c r="N10" s="30" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="62" t="inlineStr">
         <is>
           <t>22.08.2026</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="44" t="inlineStr">
         <is>
           <t>Демонтаж и зачистка</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="44" t="inlineStr">
         <is>
           <t>Оплата работы бригады (4 чел., 28 чел.-час, спуск с 5 этажа)</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="45" t="n">
         <v>20000</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="46" t="n">
         <v>16000</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="47">
         <f>E11-F11</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="63">
         <f>IFERROR(G11/E11, 0)</f>
         <v/>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="44" t="inlineStr">
         <is>
           <t>Бригада разнорабочих</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="44" t="inlineStr">
         <is>
           <t>4 чел., 28 ч.-час, экономия от рынка ~4 000 ₽</t>
         </is>
@@ -1381,45 +1581,45 @@
       <c r="M11" s="30" t="n"/>
       <c r="N11" s="30" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="64" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="64" t="inlineStr">
         <is>
           <t>23.08.2026</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>Расходные материалы</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="49" t="inlineStr">
         <is>
           <t>Мешки для пылесоса синт. 12л (5 шт) — Леруа/Лемана</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="50" t="n">
         <v>717</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="51" t="n">
         <v>717</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="47">
         <f>E12-F12</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="63">
         <f>IFERROR(G12/E12, 0)</f>
         <v/>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="49" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="49" t="inlineStr">
         <is>
           <t>Чек 3831 от 23.08.2026 11:05</t>
         </is>
@@ -1429,45 +1629,45 @@
       <c r="M12" s="30" t="n"/>
       <c r="N12" s="30" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="62" t="inlineStr">
         <is>
           <t>23.08.2026</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="44" t="inlineStr">
         <is>
           <t>Инструмент и расходники</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="44" t="inlineStr">
         <is>
           <t>Лом-гвоздодер, мешки 15шт, лента, перчатки 6п, опрыскиватель</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="45" t="n">
         <v>1830</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="46" t="n">
         <v>1830</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="47">
         <f>E13-F13</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="63">
         <f>IFERROR(G13/E13, 0)</f>
         <v/>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="44" t="inlineStr">
         <is>
           <t>ООО Ле Монлид (Лемана ПРО)</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="44" t="inlineStr">
         <is>
           <t>Чек 3832 от 23.08.2026 11:07</t>
         </is>
@@ -1477,45 +1677,45 @@
       <c r="M13" s="30" t="n"/>
       <c r="N13" s="30" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="64" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="64" t="inlineStr">
         <is>
           <t>23.08.2026</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>IT / AI-инфраструктура</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="49" t="inlineStr">
         <is>
           <t>Пополнение баланса OpenRouter (AI-ассистент Hermes)</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="50" t="n">
         <v>3000</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="51" t="n">
         <v>3000</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="47">
         <f>E14-F14</f>
         <v/>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="63">
         <f>IFERROR(G14/E14, 0)</f>
         <v/>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="49" t="inlineStr">
         <is>
           <t>OpenRouter</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="J14" s="49" t="inlineStr">
         <is>
           <t>Инфраструктура проектов и аналитики</t>
         </is>
@@ -1525,47 +1725,47 @@
       <c r="M14" s="30" t="n"/>
       <c r="N14" s="30" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="62" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="62" t="inlineStr">
         <is>
           <t>24.08.2026</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="44" t="inlineStr">
         <is>
           <t>Сантехника / Инженерия</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Счётчик воды + кран на ввод (замена закисшей запорной арматуры)</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="n">
+      <c r="D15" s="44" t="inlineStr">
+        <is>
+          <t>Счётчик воды + кран на ввод (материалы)</t>
+        </is>
+      </c>
+      <c r="E15" s="45" t="n">
         <v>2100</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="46" t="n">
         <v>2100</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="47">
         <f>E15-F15</f>
         <v/>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="63">
         <f>IFERROR(G15/E15, 0)</f>
         <v/>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="44" t="inlineStr">
         <is>
           <t>Вадим (сантехник УК)</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>Замена запорной арматуры на вводе воды в квартиру (всё закисло)</t>
+      <c r="J15" s="44" t="inlineStr">
+        <is>
+          <t>Покупка материалов для замены закисшей запорной арматуры и счётчика</t>
         </is>
       </c>
       <c r="K15" s="30" t="n"/>
@@ -1573,45 +1773,45 @@
       <c r="M15" s="30" t="n"/>
       <c r="N15" s="30" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="n">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="64" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="64" t="inlineStr">
         <is>
           <t>24.08.2026</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="49" t="inlineStr">
         <is>
           <t>Газ / Дымоход</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="49" t="inlineStr">
         <is>
           <t>Акт ВДПО — проверка дымохода и вентканала</t>
         </is>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="50" t="n">
         <v>1500</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="51" t="n">
         <v>1500</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="47">
         <f>E16-F16</f>
         <v/>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="63">
         <f>IFERROR(G16/E16, 0)</f>
         <v/>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="49" t="inlineStr">
         <is>
           <t>ВДПО / Газовая служба</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J16" s="49" t="inlineStr">
         <is>
           <t>Обязательная проверка тяги для согласования газа при ремонте</t>
         </is>
@@ -1621,45 +1821,45 @@
       <c r="M16" s="30" t="n"/>
       <c r="N16" s="30" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="62" t="inlineStr">
         <is>
           <t>24.08.2026</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="44" t="inlineStr">
         <is>
           <t>Газ / Дымоход</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="44" t="inlineStr">
         <is>
           <t>Оплата квитанций Тулагоргаз (платежки)</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="45" t="n">
         <v>800</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="46" t="n">
         <v>800</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="47">
         <f>E17-F17</f>
         <v/>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="63">
         <f>IFERROR(G17/E17, 0)</f>
         <v/>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="44" t="inlineStr">
         <is>
           <t>Тулагоргаз</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="44" t="inlineStr">
         <is>
           <t>Оплата начислений / услуг газоснабжения</t>
         </is>
@@ -1669,97 +1869,225 @@
       <c r="M17" s="30" t="n"/>
       <c r="N17" s="30" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="34" t="n"/>
-      <c r="B18" s="34" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДОВ:</t>
-        </is>
-      </c>
-      <c r="E18" s="20">
-        <f>SUM(E5:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="20">
-        <f>SUM(F5:F17)</f>
-        <v/>
-      </c>
-      <c r="G18" s="20">
-        <f>SUM(G5:G17)</f>
-        <v/>
-      </c>
-      <c r="H18" s="21">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="64" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="64" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="C18" s="49" t="inlineStr">
+        <is>
+          <t>Сантехника / Инженерия</t>
+        </is>
+      </c>
+      <c r="D18" s="49" t="inlineStr">
+        <is>
+          <t>Покупка и установка счётчика и кранов (доплата)</t>
+        </is>
+      </c>
+      <c r="E18" s="50" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F18" s="51" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G18" s="47">
+        <f>E18-F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="63">
         <f>IFERROR(G18/E18, 0)</f>
         <v/>
       </c>
-      <c r="I18" s="35" t="n"/>
-      <c r="J18" s="35" t="n"/>
+      <c r="I18" s="49" t="inlineStr">
+        <is>
+          <t>Вадим (сантехник УК)</t>
+        </is>
+      </c>
+      <c r="J18" s="49" t="inlineStr">
+        <is>
+          <t>Доплата за покупку комплектующих и установку запорной арматуры/счётчика</t>
+        </is>
+      </c>
       <c r="K18" s="30" t="n"/>
       <c r="L18" s="30" t="n"/>
       <c r="M18" s="30" t="n"/>
       <c r="N18" s="30" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="30" t="n"/>
-      <c r="B19" s="30" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="31" t="n"/>
-      <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="33" t="n"/>
-      <c r="I19" s="30" t="n"/>
-      <c r="J19" s="30" t="n"/>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="62" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="62" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="inlineStr">
+        <is>
+          <t>Двери и входная группа</t>
+        </is>
+      </c>
+      <c r="D19" s="44" t="inlineStr">
+        <is>
+          <t>Покупка входной металлической двери с внутренней МДФ-панелью</t>
+        </is>
+      </c>
+      <c r="E19" s="45" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F19" s="46" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G19" s="47">
+        <f>E19-F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="63">
+        <f>IFERROR(G19/E19, 0)</f>
+        <v/>
+      </c>
+      <c r="I19" s="44" t="inlineStr">
+        <is>
+          <t>Владимир (двери)</t>
+        </is>
+      </c>
+      <c r="J19" s="44" t="inlineStr">
+        <is>
+          <t>Входная дверь металл 1.5мм, МДФ светлый, замки Гардиан (выгода 6 000 ₽)</t>
+        </is>
+      </c>
       <c r="K19" s="30" t="n"/>
       <c r="L19" s="30" t="n"/>
       <c r="M19" s="30" t="n"/>
       <c r="N19" s="30" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="30" t="n"/>
-      <c r="B20" s="30" t="n"/>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="30" t="n"/>
-      <c r="G20" s="30" t="n"/>
-      <c r="H20" s="30" t="n"/>
-      <c r="I20" s="30" t="n"/>
-      <c r="J20" s="30" t="n"/>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="64" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="64" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
+        <is>
+          <t>Двери и входная группа</t>
+        </is>
+      </c>
+      <c r="D20" s="49" t="inlineStr">
+        <is>
+          <t>Доставка входной двери на объект</t>
+        </is>
+      </c>
+      <c r="E20" s="50" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F20" s="51" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G20" s="47">
+        <f>E20-F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="63">
+        <f>IFERROR(G20/E20, 0)</f>
+        <v/>
+      </c>
+      <c r="I20" s="49" t="inlineStr">
+        <is>
+          <t>Владимир / Доставка</t>
+        </is>
+      </c>
+      <c r="J20" s="49" t="inlineStr">
+        <is>
+          <t>Доставка двери на ул. Фрунзе 17</t>
+        </is>
+      </c>
       <c r="K20" s="30" t="n"/>
       <c r="L20" s="30" t="n"/>
       <c r="M20" s="30" t="n"/>
       <c r="N20" s="30" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="30" t="n"/>
-      <c r="B21" s="30" t="n"/>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="30" t="n"/>
-      <c r="H21" s="30" t="n"/>
-      <c r="I21" s="30" t="n"/>
-      <c r="J21" s="30" t="n"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="62" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="62" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="inlineStr">
+        <is>
+          <t>Электрика / Материалы</t>
+        </is>
+      </c>
+      <c r="D21" s="44" t="inlineStr">
+        <is>
+          <t>Черновые материалы электрики (без кабеля: щит, автоматы, подрозетники)</t>
+        </is>
+      </c>
+      <c r="E21" s="45" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F21" s="46" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G21" s="47">
+        <f>E21-F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="63">
+        <f>IFERROR(G21/E21, 0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="44" t="inlineStr">
+        <is>
+          <t>Поставщик / Электрик</t>
+        </is>
+      </c>
+      <c r="J21" s="44" t="inlineStr">
+        <is>
+          <t>Щит 18 мод, УЗО, дифавтомат, автоматы B16/B10, подрозетники, гофра, клипсы (без кабеля)</t>
+        </is>
+      </c>
       <c r="K21" s="30" t="n"/>
       <c r="L21" s="30" t="n"/>
       <c r="M21" s="30" t="n"/>
       <c r="N21" s="30" t="n"/>
     </row>
-    <row r="22">
-      <c r="A22" s="30" t="n"/>
-      <c r="B22" s="30" t="n"/>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="30" t="n"/>
-      <c r="G22" s="30" t="n"/>
-      <c r="H22" s="30" t="n"/>
-      <c r="I22" s="30" t="n"/>
-      <c r="J22" s="30" t="n"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="57" t="n"/>
+      <c r="B22" s="57" t="n"/>
+      <c r="C22" s="57" t="n"/>
+      <c r="D22" s="65" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДОВ:</t>
+        </is>
+      </c>
+      <c r="E22" s="55">
+        <f>SUM(E5:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="55">
+        <f>SUM(F5:F21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="55">
+        <f>SUM(G5:G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="66">
+        <f>IFERROR(G22/E22, 0)</f>
+        <v/>
+      </c>
+      <c r="I22" s="57" t="n"/>
+      <c r="J22" s="57" t="n"/>
       <c r="K22" s="30" t="n"/>
       <c r="L22" s="30" t="n"/>
       <c r="M22" s="30" t="n"/>
@@ -1876,6 +2204,246 @@
       <c r="L29" s="30" t="n"/>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="n"/>
+      <c r="B30" s="30" t="n"/>
+      <c r="C30" s="30" t="n"/>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="30" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="30" t="n"/>
+      <c r="H30" s="30" t="n"/>
+      <c r="I30" s="30" t="n"/>
+      <c r="J30" s="30" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
+      <c r="M30" s="30" t="n"/>
+      <c r="N30" s="30" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="30" t="n"/>
+      <c r="C31" s="30" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="30" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+      <c r="H31" s="30" t="n"/>
+      <c r="I31" s="30" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
+      <c r="M31" s="30" t="n"/>
+      <c r="N31" s="30" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="n"/>
+      <c r="B32" s="30" t="n"/>
+      <c r="C32" s="30" t="n"/>
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="30" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="30" t="n"/>
+      <c r="H32" s="30" t="n"/>
+      <c r="I32" s="30" t="n"/>
+      <c r="J32" s="30" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
+      <c r="M32" s="30" t="n"/>
+      <c r="N32" s="30" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="n"/>
+      <c r="B33" s="30" t="n"/>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="30" t="n"/>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="30" t="n"/>
+      <c r="H33" s="30" t="n"/>
+      <c r="I33" s="30" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
+      <c r="M33" s="30" t="n"/>
+      <c r="N33" s="30" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="n"/>
+      <c r="B34" s="30" t="n"/>
+      <c r="C34" s="30" t="n"/>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="30" t="n"/>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="30" t="n"/>
+      <c r="H34" s="30" t="n"/>
+      <c r="I34" s="30" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
+      <c r="M34" s="30" t="n"/>
+      <c r="N34" s="30" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="n"/>
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="30" t="n"/>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="30" t="n"/>
+      <c r="H35" s="30" t="n"/>
+      <c r="I35" s="30" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
+      <c r="M35" s="30" t="n"/>
+      <c r="N35" s="30" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="n"/>
+      <c r="B36" s="30" t="n"/>
+      <c r="C36" s="30" t="n"/>
+      <c r="D36" s="30" t="n"/>
+      <c r="E36" s="30" t="n"/>
+      <c r="F36" s="30" t="n"/>
+      <c r="G36" s="30" t="n"/>
+      <c r="H36" s="30" t="n"/>
+      <c r="I36" s="30" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
+      <c r="M36" s="30" t="n"/>
+      <c r="N36" s="30" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="30" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="30" t="n"/>
+      <c r="E37" s="30" t="n"/>
+      <c r="F37" s="30" t="n"/>
+      <c r="G37" s="30" t="n"/>
+      <c r="H37" s="30" t="n"/>
+      <c r="I37" s="30" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
+      <c r="M37" s="30" t="n"/>
+      <c r="N37" s="30" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="n"/>
+      <c r="B38" s="30" t="n"/>
+      <c r="C38" s="30" t="n"/>
+      <c r="D38" s="30" t="n"/>
+      <c r="E38" s="30" t="n"/>
+      <c r="F38" s="30" t="n"/>
+      <c r="G38" s="30" t="n"/>
+      <c r="H38" s="30" t="n"/>
+      <c r="I38" s="30" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
+      <c r="M38" s="30" t="n"/>
+      <c r="N38" s="30" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="n"/>
+      <c r="B39" s="30" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="30" t="n"/>
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="30" t="n"/>
+      <c r="H39" s="30" t="n"/>
+      <c r="I39" s="30" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
+      <c r="M39" s="30" t="n"/>
+      <c r="N39" s="30" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="n"/>
+      <c r="B40" s="30" t="n"/>
+      <c r="C40" s="30" t="n"/>
+      <c r="D40" s="30" t="n"/>
+      <c r="E40" s="30" t="n"/>
+      <c r="F40" s="30" t="n"/>
+      <c r="G40" s="30" t="n"/>
+      <c r="H40" s="30" t="n"/>
+      <c r="I40" s="30" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
+      <c r="M40" s="30" t="n"/>
+      <c r="N40" s="30" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="30" t="n"/>
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="30" t="n"/>
+      <c r="F41" s="30" t="n"/>
+      <c r="G41" s="30" t="n"/>
+      <c r="H41" s="30" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
+      <c r="M41" s="30" t="n"/>
+      <c r="N41" s="30" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="n"/>
+      <c r="B42" s="30" t="n"/>
+      <c r="C42" s="30" t="n"/>
+      <c r="D42" s="30" t="n"/>
+      <c r="E42" s="30" t="n"/>
+      <c r="F42" s="30" t="n"/>
+      <c r="G42" s="30" t="n"/>
+      <c r="H42" s="30" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
+      <c r="M42" s="30" t="n"/>
+      <c r="N42" s="30" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="n"/>
+      <c r="B43" s="30" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="30" t="n"/>
+      <c r="E43" s="30" t="n"/>
+      <c r="F43" s="30" t="n"/>
+      <c r="G43" s="30" t="n"/>
+      <c r="H43" s="30" t="n"/>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
+      <c r="M43" s="30" t="n"/>
+      <c r="N43" s="30" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="30" t="n"/>
+      <c r="B44" s="30" t="n"/>
+      <c r="C44" s="30" t="n"/>
+      <c r="D44" s="30" t="n"/>
+      <c r="E44" s="30" t="n"/>
+      <c r="F44" s="30" t="n"/>
+      <c r="G44" s="30" t="n"/>
+      <c r="H44" s="30" t="n"/>
+      <c r="I44" s="30" t="n"/>
+      <c r="J44" s="30" t="n"/>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
+      <c r="M44" s="30" t="n"/>
+      <c r="N44" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1902,468 +2470,468 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>СМЕТНЫЙ ПЛАН: РЫНОЧНАЯ СТОИМОСТЬ VS ЦЕЛЕВОЙ БЮДЖЕТ</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Сравнение среднерыночных цен Тулы с нашей целевой стоимостью выполнения</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="43" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>Этап / Раздел работ</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>Объём / Ед.</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Рынок Тула (₽)</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>Наш план / Цель (₽)</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>Плановая выгода (₽)</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="43" t="inlineStr">
         <is>
           <t>Статус выполнения</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>Способ оптимизации ниже рынка</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="n">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>1. Демонтаж, зачистка стен, вывоз мусора (8м³)</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>43.2 м²</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="45" t="n">
         <v>65000</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="46" t="n">
         <v>45000</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="47">
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="53" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>Своими силами / прямые разнорабочие</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="n">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>2. Входная дверь металлическая с МДФ + монтаж</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="64" t="inlineStr">
         <is>
           <t>1 шт</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="50" t="n">
         <v>35000</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="51" t="n">
         <v>25000</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="47">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="67" t="inlineStr">
         <is>
           <t>План</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="49" t="inlineStr">
         <is>
           <t>Оптовый поставщик в Туле</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="n">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="62" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>3. Электрика ГОСТ ВВГнг-LS (32 точки + щит 18м)</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="45" t="n">
         <v>100000</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="46" t="n">
         <v>75000</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="47">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="68" t="inlineStr">
         <is>
           <t>ТЗ готово</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="44" t="inlineStr">
         <is>
           <t>Трассировка по потолку без лишних штроб</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="11" t="n">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>4. Сантехника (разводка PPR, инсталляция, ванна 150)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="64" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="50" t="n">
         <v>120000</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="51" t="n">
         <v>90000</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="47">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="67" t="inlineStr">
         <is>
           <t>План</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="49" t="inlineStr">
         <is>
           <t>Стояк уже пластик; прямая закупка сантехники</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="11" t="n">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="62" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>5. Перепланировка гардеробной (зашивка + проём)</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="45" t="n">
         <v>30000</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="46" t="n">
         <v>18000</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="47">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="69" t="inlineStr">
         <is>
           <t>План</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="44" t="inlineStr">
         <is>
           <t>ГКЛ по месту без мокрых процессов</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="64" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>6. Черновая отделка (полы саморезы, штукатурка с/у)</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="64" t="inlineStr">
         <is>
           <t>43.2 м²</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="50" t="n">
         <v>95000</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="51" t="n">
         <v>70000</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="47">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="67" t="inlineStr">
         <is>
           <t>План</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="49" t="inlineStr">
         <is>
           <t>Без заливки стяжки (протяжка лаг)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="62" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>7. Чистовая отделка (обои, ламинат 33кл, плинтус)</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>43.2 м²</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="45" t="n">
         <v>140000</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="46" t="n">
         <v>110000</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="47">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="69" t="inlineStr">
         <is>
           <t>План</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="44" t="inlineStr">
         <is>
           <t>Светлый сканди-стандарт, единый контур</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="64" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="49" t="inlineStr">
         <is>
           <t>8. Натяжные матовые потолки + споты (вся кв.)</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="64" t="inlineStr">
         <is>
           <t>43.2 м²</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="50" t="n">
         <v>45000</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="51" t="n">
         <v>35000</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="47">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="67" t="inlineStr">
         <is>
           <t>План</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="49" t="inlineStr">
         <is>
           <t>Прямой замер от бригады потолочников</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="62" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>9. Межкомнатные двери (3 шт глухие + доборы)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="62" t="inlineStr">
         <is>
           <t>3 компл</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="45" t="n">
         <v>50000</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="46" t="n">
         <v>38000</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="47">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="69" t="inlineStr">
         <is>
           <t>План</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="44" t="inlineStr">
         <is>
           <t>Светлые царговые полотна с магнитными замками</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="64" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="49" t="inlineStr">
         <is>
           <t>10. Кухонный гарнитур + фартук + мойка/смеситель</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="64" t="inlineStr">
         <is>
           <t>1 компл</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="50" t="n">
         <v>95000</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="51" t="n">
         <v>75000</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="47">
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="67" t="inlineStr">
         <is>
           <t>План</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="49" t="inlineStr">
         <is>
           <t>Модульная кухня с интеграцией колонки Mora</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="62" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>11. Стейджинг, освещение, декор, клининг</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="62" t="inlineStr">
         <is>
           <t>комплекс</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="45" t="n">
         <v>50000</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="46" t="n">
         <v>40000</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="47">
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="69" t="inlineStr">
         <is>
           <t>План</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="44" t="inlineStr">
         <is>
           <t>Минималистичный интерьерный декор</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="14" t="n"/>
-      <c r="B16" s="19" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="57" t="n"/>
+      <c r="B16" s="65" t="inlineStr">
         <is>
           <t>ИТОГО СМЕТА РЕМОНТА:</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="20">
+      <c r="C16" s="57" t="n"/>
+      <c r="D16" s="55">
         <f>SUM(D5:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="55">
         <f>SUM(E5:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="56">
         <f>SUM(F5:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
+      <c r="G16" s="57" t="n"/>
+      <c r="H16" s="57" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -18,12 +18,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00 &quot;₽&quot;"/>
+    <numFmt numFmtId="167" formatCode="+0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -137,8 +138,49 @@
       <color rgb="000284C7"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -181,8 +223,14 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -315,11 +363,179 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000F172A"/>
+      </left>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000F172A"/>
+      </right>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -487,6 +703,257 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -853,306 +1320,1144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="38" t="inlineStr">
-        <is>
-          <t>ИНВЕСТИЦИОННАЯ СВОДКА И ДАШБОРД ПРОЕКТА</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>Флиппинг 2-комн. квартиры: г. Тула, ул. Фрунзе 17, кв. 76 (43.2 м²)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Покупка объекта
-3 900 000 ₽</t>
-        </is>
-      </c>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Бюджет ремонта (план)
-618 000 ₽</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Целевая продажа
-5 600 000 ₽</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Плановая чистая прибыль
-≈ 1 062 000 ₽</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="n"/>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="23" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="23" t="n"/>
-      <c r="H5" s="24" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="40" t="inlineStr">
-        <is>
-          <t>ФИНАНСОВЫЙ БАЛАНС И СРАВНЕНИЕ С РЫНКОМ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="41" t="inlineStr">
-        <is>
-          <t>Статья бюджета / Показатель</t>
-        </is>
-      </c>
-      <c r="B10" s="42" t="inlineStr">
-        <is>
-          <t>Рыночный ориентир (₽)</t>
-        </is>
-      </c>
-      <c r="C10" s="42" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="74" t="inlineStr">
+        <is>
+          <t>ИНВЕСТИЦИОННЫЙ ДАШБОРД И СВОДКА ПРОЕКТА — ФРУНЗЕ 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="116" t="inlineStr">
+        <is>
+          <t>Объект: г. Тула, ул. Фрунзе 17, кв. 76 (2-комн., 43.2 м², 5/5 эт.) | Стратегия: Флиппинг (цикл 2 месяца)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="117" t="inlineStr">
+        <is>
+          <t>ПОКУПКА ОБЪЕКТА</t>
+        </is>
+      </c>
+      <c r="B4" s="117" t="n"/>
+      <c r="C4" s="117" t="inlineStr">
+        <is>
+          <t>БЮДЖЕТ РЕМОНТА</t>
+        </is>
+      </c>
+      <c r="D4" s="117" t="inlineStr">
+        <is>
+          <t>ФАКТ ВЛОЖЕНО</t>
+        </is>
+      </c>
+      <c r="E4" s="117" t="inlineStr">
+        <is>
+          <t>ТАРГЕТ ПРОДАЖИ</t>
+        </is>
+      </c>
+      <c r="F4" s="117" t="inlineStr">
+        <is>
+          <t>ПЛАН. ПРИБЫЛЬ</t>
+        </is>
+      </c>
+      <c r="G4" s="117" t="inlineStr">
+        <is>
+          <t>ПЛАН. ROI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="118" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="B5" s="119" t="n"/>
+      <c r="C5" s="118">
+        <f>'План vs Рынок (Смета)'!E16</f>
+        <v/>
+      </c>
+      <c r="D5" s="118">
+        <f>'Факт расходов'!F32</f>
+        <v/>
+      </c>
+      <c r="E5" s="118" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="F5" s="120">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="G5" s="121">
+        <f>C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="160" t="inlineStr">
+        <is>
+          <t>1. ИНВЕСТИЦИОННАЯ МОДЕЛЬ СДЕЛКИ (ПОЛНАЯ СЕБЕСТОИМОСТЬ И ДОХОДНОСТЬ)</t>
+        </is>
+      </c>
+      <c r="B8" s="122" t="n"/>
+      <c r="C8" s="122" t="n"/>
+      <c r="D8" s="122" t="n"/>
+      <c r="E8" s="122" t="n"/>
+      <c r="F8" s="122" t="n"/>
+      <c r="G8" s="122" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>Статья инвестиций / Показатель</t>
+        </is>
+      </c>
+      <c r="B9" s="42" t="inlineStr">
+        <is>
+          <t>Рынок / Базовый план (₽)</t>
+        </is>
+      </c>
+      <c r="C9" s="42" t="inlineStr">
         <is>
           <t>Наш план / Факт (₽)</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr">
-        <is>
-          <t>Экономия за счёт оптимизации (₽)</t>
-        </is>
-      </c>
-      <c r="E10" s="43" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>Экономия / Выгода (₽)</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
+      <c r="F9" s="41" t="inlineStr">
+        <is>
+          <t>Примечание / Обоснование</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t>1.1. Стоимость покупки объекта</t>
+        </is>
+      </c>
+      <c r="B10" s="50" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="C10" s="51" t="n">
+        <v>3900000</v>
+      </c>
+      <c r="D10" s="123">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="64" t="inlineStr">
+        <is>
+          <t>Оплачено</t>
+        </is>
+      </c>
+      <c r="F10" s="49" t="inlineStr">
+        <is>
+          <t>Базовый актив, договор купли-продажи</t>
+        </is>
+      </c>
+      <c r="G10" s="49" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>1. Стоимость покупки квартиры</t>
+          <t>1.2. Юр. оформление, пошлина, доступ, IT</t>
         </is>
       </c>
       <c r="B11" s="45" t="n">
-        <v>3900000</v>
-      </c>
-      <c r="C11" s="46" t="n">
-        <v>3900000</v>
-      </c>
-      <c r="D11" s="47">
+        <v>23000</v>
+      </c>
+      <c r="C11" s="46">
+        <f>SUMIF('Факт расходов'!C5:C31, "*Юр.*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*Безопасность*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*IT*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*Электроэнергия*", 'Факт расходов'!F5:F31)</f>
+        <v/>
+      </c>
+      <c r="D11" s="124">
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="48" t="inlineStr">
+      <c r="E11" s="62" t="inlineStr">
         <is>
           <t>Оплачено</t>
         </is>
       </c>
+      <c r="F11" s="44" t="inlineStr">
+        <is>
+          <t>ЭЦП (7к), Росреестр (5к), вскрытие (8к), AI (3к)</t>
+        </is>
+      </c>
+      <c r="G11" s="44" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="49" t="inlineStr">
         <is>
-          <t>2. Начальные расходы (ЭЦП, госпошлина, вскрытие)</t>
-        </is>
-      </c>
-      <c r="B12" s="50" t="n">
-        <v>20000</v>
+          <t>1.3. Бюджет ремонта, стейджинга и клининга</t>
+        </is>
+      </c>
+      <c r="B12" s="50">
+        <f>'План vs Рынок (Смета)'!D16</f>
+        <v/>
       </c>
       <c r="C12" s="51">
-        <f>'Факт расходов'!F22</f>
-        <v/>
-      </c>
-      <c r="D12" s="47">
+        <f>'План vs Рынок (Смета)'!E16</f>
+        <v/>
+      </c>
+      <c r="D12" s="123">
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="52" t="inlineStr">
-        <is>
-          <t>Оплачено</t>
-        </is>
-      </c>
+      <c r="E12" s="64" t="inlineStr">
+        <is>
+          <t>В процессе</t>
+        </is>
+      </c>
+      <c r="F12" s="49" t="inlineStr">
+        <is>
+          <t>Смета по 11 этапам (цель 621 000 ₽ vs рынок 825 000 ₽)</t>
+        </is>
+      </c>
+      <c r="G12" s="49" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
         <is>
-          <t>3. Смета ремонта и чистовой отделки</t>
-        </is>
-      </c>
-      <c r="B13" s="45">
-        <f>'План vs Рынок (Смета)'!D16</f>
-        <v/>
-      </c>
-      <c r="C13" s="46">
-        <f>'План vs Рынок (Смета)'!E16</f>
-        <v/>
-      </c>
-      <c r="D13" s="47">
+          <t>1.4. Резерв на непредвиденные расходы</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="124">
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="53" t="inlineStr">
+      <c r="E13" s="62" t="inlineStr">
+        <is>
+          <t>В резерве</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t>Запас прочности на скрытые дефекты</t>
+        </is>
+      </c>
+      <c r="G13" s="44" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="54" t="inlineStr">
+        <is>
+          <t>ИТОГО ПЛАНОВАЯ СЕБЕСТОИМОСТЬ ОБЪЕКТА:</t>
+        </is>
+      </c>
+      <c r="B14" s="55">
+        <f>SUM(B10:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="55">
+        <f>SUM(C10:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="55">
+        <f>SUM(D10:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="94" t="inlineStr">
+        <is>
+          <t>План</t>
+        </is>
+      </c>
+      <c r="F14" s="125" t="inlineStr">
+        <is>
+          <t>Покупка (3.9М) + юристы (23к) + смета ремонта (621к)</t>
+        </is>
+      </c>
+      <c r="G14" s="125" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="126" t="inlineStr">
+        <is>
+          <t>ТЕКУЩИЙ ФАКТ ОПЛАЧЕННЫХ СРЕДСТВ НА СЕГОДНЯ:</t>
+        </is>
+      </c>
+      <c r="B15" s="127" t="n">
+        <v>3923000</v>
+      </c>
+      <c r="C15" s="127">
+        <f>C10+C11+C37</f>
+        <v/>
+      </c>
+      <c r="D15" s="127">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="128" t="inlineStr">
+        <is>
+          <t>Факт</t>
+        </is>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
+        <is>
+          <t>Покупка 3.9М + оформление 23к + факт ремонта 96.7к</t>
+        </is>
+      </c>
+      <c r="G15" s="44" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="129" t="inlineStr">
+        <is>
+          <t>ЦЕЛЕВАЯ ВЫРУЧКА ОТ ПРОДАЖИ (ТАРГЕТ):</t>
+        </is>
+      </c>
+      <c r="B16" s="130" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="C16" s="130" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="D16" s="130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="132" t="inlineStr">
+        <is>
+          <t>Таргет</t>
+        </is>
+      </c>
+      <c r="F16" s="49" t="inlineStr">
+        <is>
+          <t>129 630 ₽/м² (верхняя планка Советского р-на)</t>
+        </is>
+      </c>
+      <c r="G16" s="49" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="126" t="inlineStr">
+        <is>
+          <t>ПЛАНОВАЯ ЧИСТАЯ ПРИБЫЛЬ ИНВЕСТОРА:</t>
+        </is>
+      </c>
+      <c r="B17" s="127">
+        <f>B16-B14</f>
+        <v/>
+      </c>
+      <c r="C17" s="124">
+        <f>C16-C14</f>
+        <v/>
+      </c>
+      <c r="D17" s="124">
+        <f>C17-B17</f>
+        <v/>
+      </c>
+      <c r="E17" s="128" t="inlineStr">
+        <is>
+          <t>Прибыль</t>
+        </is>
+      </c>
+      <c r="F17" s="44" t="inlineStr">
+        <is>
+          <t>Чистый финансовый результат по итогам проекта</t>
+        </is>
+      </c>
+      <c r="G17" s="44" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="129" t="inlineStr">
+        <is>
+          <t>РЕНТАБЕЛЬНОСТЬ ИНВЕСТИЦИЙ (ROI НА ЦИКЛ):</t>
+        </is>
+      </c>
+      <c r="B18" s="133">
+        <f>(B16-B14)/B14</f>
+        <v/>
+      </c>
+      <c r="C18" s="134">
+        <f>C17/C14</f>
+        <v/>
+      </c>
+      <c r="D18" s="134">
+        <f>C18-B18</f>
+        <v/>
+      </c>
+      <c r="E18" s="132" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
+      <c r="F18" s="49" t="inlineStr">
+        <is>
+          <t>Доходность капитала за 2 месяца</t>
+        </is>
+      </c>
+      <c r="G18" s="49" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="160" t="inlineStr">
+        <is>
+          <t>2. ОПЕРАЦИОННЫЙ ТРЕКЕР БЮДЖЕТА РЕМОНТА (ПЛАН VS ФАКТ VS ОСТАТОК)</t>
+        </is>
+      </c>
+      <c r="B21" s="122" t="n"/>
+      <c r="C21" s="122" t="n"/>
+      <c r="D21" s="122" t="n"/>
+      <c r="E21" s="122" t="n"/>
+      <c r="F21" s="122" t="n"/>
+      <c r="G21" s="122" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>Раздел сметы / Вид работ</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>План сметы (₽)</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>Факт оплачено (₽)</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
+        <is>
+          <t>Остаток к оплате (₽)</t>
+        </is>
+      </c>
+      <c r="E22" s="43" t="inlineStr">
+        <is>
+          <t>Освоено</t>
+        </is>
+      </c>
+      <c r="F22" s="41" t="inlineStr">
+        <is>
+          <t>Статус выполнения</t>
+        </is>
+      </c>
+      <c r="G22" s="41" t="inlineStr">
+        <is>
+          <t>Текущий факт / Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>1. Демонтаж, зачистка, вывоз мусора</t>
+        </is>
+      </c>
+      <c r="B23" s="45">
+        <f>'План vs Рынок (Смета)'!E5</f>
+        <v/>
+      </c>
+      <c r="C23" s="46">
+        <f>SUMIF('Факт расходов'!C5:C31, "*Демонтаж*", 'Факт расходов'!F5:F31)</f>
+        <v/>
+      </c>
+      <c r="D23" s="45">
+        <f>B23-C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="135">
+        <f>IFERROR(C23/B23, 0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="62" t="inlineStr">
+        <is>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="G23" s="44" t="inlineStr">
+        <is>
+          <t>Контейнер 8.5к + сосед 1к + бригада 16к (25.5к)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="49" t="inlineStr">
+        <is>
+          <t>2. Входная группа (дверь, доставка, монтаж)</t>
+        </is>
+      </c>
+      <c r="B24" s="50">
+        <f>'План vs Рынок (Смета)'!E6</f>
+        <v/>
+      </c>
+      <c r="C24" s="51">
+        <f>SUMIF('Факт расходов'!C5:C31, "*Двери*", 'Факт расходов'!F5:F31)</f>
+        <v/>
+      </c>
+      <c r="D24" s="50">
+        <f>B24-C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="136">
+        <f>IFERROR(C24/B24, 0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="64" t="inlineStr">
+        <is>
+          <t>Выполнено</t>
+        </is>
+      </c>
+      <c r="G24" s="49" t="inlineStr">
+        <is>
+          <t>Дверь 16к + доставка 1.5к + монтаж 9к (26.5к под ключ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>3. Электрика ГОСТ (материалы + работы)</t>
+        </is>
+      </c>
+      <c r="B25" s="45">
+        <f>'План vs Рынок (Смета)'!E7</f>
+        <v/>
+      </c>
+      <c r="C25" s="46">
+        <f>SUMIF('Факт расходов'!C5:C31, "*Электрика*", 'Факт расходов'!F5:F31)</f>
+        <v/>
+      </c>
+      <c r="D25" s="45">
+        <f>B25-C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="135">
+        <f>IFERROR(C25/B25, 0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="62" t="inlineStr">
+        <is>
+          <t>Разведено / Собрано</t>
+        </is>
+      </c>
+      <c r="G25" s="44" t="inlineStr">
+        <is>
+          <t>Работы 50к + материалы 48.5к (итого 98.5к под ключ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="49" t="inlineStr">
+        <is>
+          <t>4. Сантехника (разводка PPR, ванна 150)</t>
+        </is>
+      </c>
+      <c r="B26" s="50">
+        <f>'План vs Рынок (Смета)'!E8</f>
+        <v/>
+      </c>
+      <c r="C26" s="51">
+        <f>SUMIF('Факт расходов'!C5:C31, "*Сантехника*", 'Факт расходов'!F5:F31)</f>
+        <v/>
+      </c>
+      <c r="D26" s="50">
+        <f>B26-C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="136">
+        <f>IFERROR(C26/B26, 0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="64" t="inlineStr">
+        <is>
+          <t>Ввод / Стояки</t>
+        </is>
+      </c>
+      <c r="G26" s="49" t="inlineStr">
+        <is>
+          <t>Краны и счётчик 4.1к закрыты, далее трассы</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>5. Газ и вентиляция (ВДПО, квитанции, срезка)</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C27" s="46">
+        <f>SUMIF('Факт расходов'!C5:C31, "*Газ*", 'Факт расходов'!F5:F31)</f>
+        <v/>
+      </c>
+      <c r="D27" s="45">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="135">
+        <f>IFERROR(C27/B27, 0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="62" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="G27" s="44" t="inlineStr">
+        <is>
+          <t>Акт ВДПО 1.5к + платежки 0.8к закрыты</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="49" t="inlineStr">
+        <is>
+          <t>6. Перепланировка гардеробной (ГКЛ)</t>
+        </is>
+      </c>
+      <c r="B28" s="50">
+        <f>'План vs Рынок (Смета)'!E9</f>
+        <v/>
+      </c>
+      <c r="C28" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="50">
+        <f>B28-C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="136">
+        <f>IFERROR(C28/B28, 0)</f>
+        <v/>
+      </c>
+      <c r="F28" s="64" t="inlineStr">
+        <is>
+          <t>План</t>
+        </is>
+      </c>
+      <c r="G28" s="49" t="inlineStr">
+        <is>
+          <t>Зашивка двери из зала + проем из спальни</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>7. Черновая отделка (полы саморезы, с/у)</t>
+        </is>
+      </c>
+      <c r="B29" s="45">
+        <f>'План vs Рынок (Смета)'!E10</f>
+        <v/>
+      </c>
+      <c r="C29" s="46">
+        <f>SUMIF('Факт расходов'!C5:C31, "*Черновая*", 'Факт расходов'!F5:F31)</f>
+        <v/>
+      </c>
+      <c r="D29" s="45">
+        <f>B29-C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="135">
+        <f>IFERROR(C29/B29, 0)</f>
+        <v/>
+      </c>
+      <c r="F29" s="62" t="inlineStr">
+        <is>
+          <t>План</t>
+        </is>
+      </c>
+      <c r="G29" s="44" t="inlineStr">
+        <is>
+          <t>Протяжка лаг желтыми саморезами без стяжки</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="49" t="inlineStr">
+        <is>
+          <t>8. Чистовая отделка (обои греж, ламинат 33кл)</t>
+        </is>
+      </c>
+      <c r="B30" s="50">
+        <f>'План vs Рынок (Смета)'!E11</f>
+        <v/>
+      </c>
+      <c r="C30" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="50">
+        <f>B30-C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="136">
+        <f>IFERROR(C30/B30, 0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="64" t="inlineStr">
+        <is>
+          <t>План</t>
+        </is>
+      </c>
+      <c r="G30" s="49" t="inlineStr">
+        <is>
+          <t>Единый контур светлый дуб, плинтус 80мм</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>9. Натяжные матовые потолки + споты</t>
+        </is>
+      </c>
+      <c r="B31" s="45">
+        <f>'План vs Рынок (Смета)'!E12</f>
+        <v/>
+      </c>
+      <c r="C31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="45">
+        <f>B31-C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="135">
+        <f>IFERROR(C31/B31, 0)</f>
+        <v/>
+      </c>
+      <c r="F31" s="62" t="inlineStr">
+        <is>
+          <t>План</t>
+        </is>
+      </c>
+      <c r="G31" s="44" t="inlineStr">
+        <is>
+          <t>Матовый сатин, треки/споты по зонам</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="49" t="inlineStr">
+        <is>
+          <t>10. Межкомнатные двери (3 комплекта)</t>
+        </is>
+      </c>
+      <c r="B32" s="50">
+        <f>'План vs Рынок (Смета)'!E13</f>
+        <v/>
+      </c>
+      <c r="C32" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="50">
+        <f>B32-C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="136">
+        <f>IFERROR(C32/B32, 0)</f>
+        <v/>
+      </c>
+      <c r="F32" s="64" t="inlineStr">
+        <is>
+          <t>План</t>
+        </is>
+      </c>
+      <c r="G32" s="49" t="inlineStr">
+        <is>
+          <t>Белые царговые глухие полотна с магнитными замками</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>11. Кухонный гарнитур + колонка Mora</t>
+        </is>
+      </c>
+      <c r="B33" s="45">
+        <f>'План vs Рынок (Смета)'!E14</f>
+        <v/>
+      </c>
+      <c r="C33" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="45">
+        <f>B33-C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="135">
+        <f>IFERROR(C33/B33, 0)</f>
+        <v/>
+      </c>
+      <c r="F33" s="62" t="inlineStr">
+        <is>
+          <t>План</t>
+        </is>
+      </c>
+      <c r="G33" s="44" t="inlineStr">
+        <is>
+          <t>Модульная кухня с интеграцией колонки (заказ Неделя 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="49" t="inlineStr">
+        <is>
+          <t>12. Стейджинг, освещение, декор, клининг</t>
+        </is>
+      </c>
+      <c r="B34" s="50">
+        <f>'План vs Рынок (Смета)'!E15</f>
+        <v/>
+      </c>
+      <c r="C34" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="50">
+        <f>B34-C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="136">
+        <f>IFERROR(C34/B34, 0)</f>
+        <v/>
+      </c>
+      <c r="F34" s="64" t="inlineStr">
+        <is>
+          <t>План</t>
+        </is>
+      </c>
+      <c r="G34" s="49" t="inlineStr">
+        <is>
+          <t>Минималистичный интерьерный декор под верх планки</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>13. Инструмент и расходники (хозмаг/Лемана)</t>
+        </is>
+      </c>
+      <c r="B35" s="45" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C35" s="46">
+        <f>SUMIF('Факт расходов'!C5:C31, "*Инструмент*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*Расходные*", 'Факт расходов'!F5:F31)</f>
+        <v/>
+      </c>
+      <c r="D35" s="45">
+        <f>B35-C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="135">
+        <f>IFERROR(C35/B35, 0)</f>
+        <v/>
+      </c>
+      <c r="F35" s="62" t="inlineStr">
         <is>
           <t>В процессе</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="49" t="inlineStr">
-        <is>
-          <t>4. Экономия на окнах ПВХ (сохранены)</t>
-        </is>
-      </c>
-      <c r="B14" s="50" t="n">
+      <c r="G35" s="44" t="inlineStr">
+        <is>
+          <t>Лом, мешки, пылесос, перчатки (2 847 ₽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="49" t="inlineStr">
+        <is>
+          <t>14. Мелкие хозрасходы и вспомогательные траты</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C36" s="51">
+        <f>SUMIF('Факт расходов'!C5:C31, "*хозмаг*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*Хоз.*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*Оснащение*", 'Факт расходов'!F5:F31)</f>
+        <v/>
+      </c>
+      <c r="D36" s="50">
+        <f>B36-C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="136">
+        <f>IFERROR(C36/B36, 0)</f>
+        <v/>
+      </c>
+      <c r="F36" s="64" t="inlineStr">
+        <is>
+          <t>По факту</t>
+        </is>
+      </c>
+      <c r="G36" s="49" t="inlineStr">
+        <is>
+          <t>Расходники для зачистки (300 ₽)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="54" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО СМЕТЕ РЕМОНТА:</t>
+        </is>
+      </c>
+      <c r="B37" s="55">
+        <f>SUM(B23:B36)</f>
+        <v/>
+      </c>
+      <c r="C37" s="55">
+        <f>SUM(C23:C36)</f>
+        <v/>
+      </c>
+      <c r="D37" s="55">
+        <f>SUM(D23:D36)</f>
+        <v/>
+      </c>
+      <c r="E37" s="100">
+        <f>IFERROR(C37/B37, 0)</f>
+        <v/>
+      </c>
+      <c r="F37" s="137" t="inlineStr">
+        <is>
+          <t>В графике</t>
+        </is>
+      </c>
+      <c r="G37" s="125" t="inlineStr">
+        <is>
+          <t>Текущее освоение бюджета</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="160" t="inlineStr">
+        <is>
+          <t>3. КАРТА ЭКОНОМИИ ИНВЕСТОРА (ОПТИМИЗАЦИЯ УЗЛОВ + СКИДКИ НА ЗАКУПКАХ)</t>
+        </is>
+      </c>
+      <c r="B40" s="122" t="n"/>
+      <c r="C40" s="122" t="n"/>
+      <c r="D40" s="122" t="n"/>
+      <c r="E40" s="122" t="n"/>
+      <c r="F40" s="122" t="n"/>
+      <c r="G40" s="122" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>Статья оптимизации / Инженерный узел</t>
+        </is>
+      </c>
+      <c r="B41" s="42" t="inlineStr">
+        <is>
+          <t>Рыночная цена (₽)</t>
+        </is>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
+        <is>
+          <t>Наша цена (₽)</t>
+        </is>
+      </c>
+      <c r="D41" s="42" t="inlineStr">
+        <is>
+          <t>Чистая экономия (₽)</t>
+        </is>
+      </c>
+      <c r="E41" s="43" t="inlineStr">
+        <is>
+          <t>% Выгоды</t>
+        </is>
+      </c>
+      <c r="F41" s="41" t="inlineStr">
+        <is>
+          <t>Обоснование / Способ оптимизации</t>
+        </is>
+      </c>
+      <c r="G41" s="41" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="49" t="inlineStr">
+        <is>
+          <t>3.1. Окна ПВХ (сохранены во всей квартире)</t>
+        </is>
+      </c>
+      <c r="B42" s="50" t="n">
         <v>120000</v>
       </c>
-      <c r="C14" s="51" t="n">
+      <c r="C42" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="47" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E14" s="52" t="inlineStr">
-        <is>
-          <t>Сэкономлено</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>5. Экономия на стояке канализации (сохранен)</t>
-        </is>
-      </c>
-      <c r="B15" s="45" t="n">
+      <c r="D42" s="123">
+        <f>B42-C42</f>
+        <v/>
+      </c>
+      <c r="E42" s="134">
+        <f>IFERROR(D42/B42, 0)</f>
+        <v/>
+      </c>
+      <c r="F42" s="49" t="inlineStr">
+        <is>
+          <t>Сохранены все стеклопакеты и балконный блок (регулировка + откосы)</t>
+        </is>
+      </c>
+      <c r="G42" s="49" t="n"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="44" t="inlineStr">
+        <is>
+          <t>3.2. Стояк канализации 110 мм (сохранен)</t>
+        </is>
+      </c>
+      <c r="B43" s="45" t="n">
         <v>15000</v>
       </c>
-      <c r="C15" s="46" t="n">
+      <c r="C43" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="47" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E15" s="48" t="inlineStr">
-        <is>
-          <t>Сэкономлено</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="49" t="inlineStr">
-        <is>
-          <t>6. Экономия на счётчике СОЛО (пломба 02.2024)</t>
-        </is>
-      </c>
-      <c r="B16" s="50" t="n">
-        <v>7000</v>
-      </c>
-      <c r="C16" s="51" t="n">
+      <c r="D43" s="124">
+        <f>B43-C43</f>
+        <v/>
+      </c>
+      <c r="E43" s="138">
+        <f>IFERROR(D43/B43, 0)</f>
+        <v/>
+      </c>
+      <c r="F43" s="44" t="inlineStr">
+        <is>
+          <t>Уже заменён на пластик ПВХ/ПП 110мм, перекрытия долбить не нужно</t>
+        </is>
+      </c>
+      <c r="G43" s="44" t="n"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="49" t="inlineStr">
+        <is>
+          <t>3.3. Электросчётчик (новый прибор учёта)</t>
+        </is>
+      </c>
+      <c r="B44" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="47" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E16" s="52" t="inlineStr">
-        <is>
-          <t>Сэкономлено</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="54" t="inlineStr">
-        <is>
-          <t>ВСЕГО ЗАТРАТ НА ПРОЕКТ (ПОКУПКА + РЕМОНТ):</t>
-        </is>
-      </c>
-      <c r="B18" s="55">
-        <f>B11+B12+B13</f>
-        <v/>
-      </c>
-      <c r="C18" s="55">
-        <f>C11+C12+C13</f>
-        <v/>
-      </c>
-      <c r="D18" s="56">
-        <f>D11+D12+D13+D14+D15+D16</f>
-        <v/>
-      </c>
-      <c r="E18" s="57" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Выручка от продажи (таргет):</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="58" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="59" t="inlineStr">
-        <is>
-          <t>ЧИСТАЯ ПРИБЫЛЬ ИНВЕСТОРА:</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="60">
-        <f>C20-C18</f>
-        <v/>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Рентабельность инвестиций (ROI на цикл):</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="61">
-        <f>C21/C18</f>
-        <v/>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
+      <c r="C44" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="134">
+        <f>IFERROR(D44/B44, 0)</f>
+        <v/>
+      </c>
+      <c r="F44" s="49" t="inlineStr">
+        <is>
+          <t>Новый счётчик закуплен в составе материалов (поз. 17 на 16.5к); распломбировка 2.5к закрыта</t>
+        </is>
+      </c>
+      <c r="G44" s="49" t="n"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="44" t="inlineStr">
+        <is>
+          <t>3.4. Фактическая экономия на закупках и работах</t>
+        </is>
+      </c>
+      <c r="B45" s="45">
+        <f>'Факт расходов'!E32</f>
+        <v/>
+      </c>
+      <c r="C45" s="45">
+        <f>'Факт расходов'!F32</f>
+        <v/>
+      </c>
+      <c r="D45" s="124">
+        <f>B45-C45</f>
+        <v/>
+      </c>
+      <c r="E45" s="138">
+        <f>IFERROR(D45/B45, 0)</f>
+        <v/>
+      </c>
+      <c r="F45" s="44" t="inlineStr">
+        <is>
+          <t>Скидки от поставщиков (дверь -6к, кабель -2к, мусор -0.5к, демонтаж -4к и др.)</t>
+        </is>
+      </c>
+      <c r="G45" s="44" t="n"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="54" t="inlineStr">
+        <is>
+          <t>ИТОГО СБЕРЕЖЁННЫЙ КАПИТАЛ ИНВЕСТОРА:</t>
+        </is>
+      </c>
+      <c r="B46" s="55">
+        <f>SUM(B42:B45)</f>
+        <v/>
+      </c>
+      <c r="C46" s="55">
+        <f>SUM(C42:C45)</f>
+        <v/>
+      </c>
+      <c r="D46" s="55">
+        <f>SUM(D42:D45)</f>
+        <v/>
+      </c>
+      <c r="E46" s="139">
+        <f>IFERROR(D46/B46, 0)</f>
+        <v/>
+      </c>
+      <c r="F46" s="125" t="inlineStr">
+        <is>
+          <t>Прямой вклад в повышение маржинальности сделки</t>
+        </is>
+      </c>
+      <c r="G46" s="125" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="G4:H5"/>
-    <mergeCell ref="E4:F5"/>
+  <mergeCells count="23">
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F44:G44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1164,34 +2469,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="71" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="38" t="inlineStr">
         <is>
           <t>ЖУРНАЛ ФАКТИЧЕСКИХ РАСХОДОВ — ФРУНЗЕ 17</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="K1" s="140" t="n"/>
+      <c r="L1" s="140" t="n"/>
+      <c r="M1" s="140" t="n"/>
+      <c r="N1" s="140" t="n"/>
+      <c r="O1" s="140" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Объект: г. Тула, ул. Фрунзе 17, кв. 76 (2-комн., 43.2 м²) | Флиппинг</t>
         </is>
       </c>
+      <c r="K2" s="140" t="n"/>
+      <c r="L2" s="140" t="n"/>
+      <c r="M2" s="140" t="n"/>
+      <c r="N2" s="140" t="n"/>
+      <c r="O2" s="140" t="n"/>
+    </row>
+    <row r="3">
+      <c r="K3" s="140" t="n"/>
+      <c r="L3" s="140" t="n"/>
+      <c r="M3" s="140" t="n"/>
+      <c r="N3" s="140" t="n"/>
+      <c r="O3" s="140" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="43" t="inlineStr">
@@ -1244,6 +2566,11 @@
           <t>Примечание / Чек</t>
         </is>
       </c>
+      <c r="K4" s="140" t="n"/>
+      <c r="L4" s="140" t="n"/>
+      <c r="M4" s="140" t="n"/>
+      <c r="N4" s="140" t="n"/>
+      <c r="O4" s="140" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="62" t="n">
@@ -1292,6 +2619,7 @@
       <c r="L5" s="30" t="n"/>
       <c r="M5" s="30" t="n"/>
       <c r="N5" s="30" t="n"/>
+      <c r="O5" s="140" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="64" t="n">
@@ -1340,6 +2668,7 @@
       <c r="L6" s="30" t="n"/>
       <c r="M6" s="30" t="n"/>
       <c r="N6" s="30" t="n"/>
+      <c r="O6" s="140" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="62" t="n">
@@ -1388,6 +2717,7 @@
       <c r="L7" s="30" t="n"/>
       <c r="M7" s="30" t="n"/>
       <c r="N7" s="30" t="n"/>
+      <c r="O7" s="140" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="64" t="n">
@@ -1436,6 +2766,7 @@
       <c r="L8" s="30" t="n"/>
       <c r="M8" s="30" t="n"/>
       <c r="N8" s="30" t="n"/>
+      <c r="O8" s="140" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="62" t="n">
@@ -1484,6 +2815,7 @@
       <c r="L9" s="30" t="n"/>
       <c r="M9" s="30" t="n"/>
       <c r="N9" s="30" t="n"/>
+      <c r="O9" s="140" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="64" t="n">
@@ -1532,6 +2864,7 @@
       <c r="L10" s="30" t="n"/>
       <c r="M10" s="30" t="n"/>
       <c r="N10" s="30" t="n"/>
+      <c r="O10" s="140" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="62" t="n">
@@ -1580,6 +2913,7 @@
       <c r="L11" s="30" t="n"/>
       <c r="M11" s="30" t="n"/>
       <c r="N11" s="30" t="n"/>
+      <c r="O11" s="140" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="64" t="n">
@@ -1628,6 +2962,7 @@
       <c r="L12" s="30" t="n"/>
       <c r="M12" s="30" t="n"/>
       <c r="N12" s="30" t="n"/>
+      <c r="O12" s="140" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="62" t="n">
@@ -1676,6 +3011,7 @@
       <c r="L13" s="30" t="n"/>
       <c r="M13" s="30" t="n"/>
       <c r="N13" s="30" t="n"/>
+      <c r="O13" s="140" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="64" t="n">
@@ -1724,6 +3060,7 @@
       <c r="L14" s="30" t="n"/>
       <c r="M14" s="30" t="n"/>
       <c r="N14" s="30" t="n"/>
+      <c r="O14" s="140" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="62" t="n">
@@ -1772,6 +3109,7 @@
       <c r="L15" s="30" t="n"/>
       <c r="M15" s="30" t="n"/>
       <c r="N15" s="30" t="n"/>
+      <c r="O15" s="140" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="64" t="n">
@@ -1820,6 +3158,7 @@
       <c r="L16" s="30" t="n"/>
       <c r="M16" s="30" t="n"/>
       <c r="N16" s="30" t="n"/>
+      <c r="O16" s="140" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="62" t="n">
@@ -1868,6 +3207,7 @@
       <c r="L17" s="30" t="n"/>
       <c r="M17" s="30" t="n"/>
       <c r="N17" s="30" t="n"/>
+      <c r="O17" s="140" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="64" t="n">
@@ -1916,6 +3256,7 @@
       <c r="L18" s="30" t="n"/>
       <c r="M18" s="30" t="n"/>
       <c r="N18" s="30" t="n"/>
+      <c r="O18" s="140" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="62" t="n">
@@ -1964,6 +3305,7 @@
       <c r="L19" s="30" t="n"/>
       <c r="M19" s="30" t="n"/>
       <c r="N19" s="30" t="n"/>
+      <c r="O19" s="140" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="64" t="n">
@@ -2012,6 +3354,7 @@
       <c r="L20" s="30" t="n"/>
       <c r="M20" s="30" t="n"/>
       <c r="N20" s="30" t="n"/>
+      <c r="O20" s="140" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="62" t="n">
@@ -2029,7 +3372,7 @@
       </c>
       <c r="D21" s="44" t="inlineStr">
         <is>
-          <t>Черновые материалы электрики (без кабеля: щит, автоматы, подрозетники)</t>
+          <t>Черновые материалы электрики (щит 18м, новый электросчётчик, автоматы, УЗО, подрозетники, гофра)</t>
         </is>
       </c>
       <c r="E21" s="45" t="n">
@@ -2048,210 +3391,542 @@
       </c>
       <c r="I21" s="44" t="inlineStr">
         <is>
-          <t>Поставщик / Электрик</t>
+          <t>Анатолий / Поставщик</t>
         </is>
       </c>
       <c r="J21" s="44" t="inlineStr">
         <is>
-          <t>Щит 18 мод, УЗО, дифавтомат, автоматы B16/B10, подрозетники, гофра, клипсы (без кабеля)</t>
+          <t>Щит 18 мод, новый счётчик, УЗО, дифавтомат, автоматы B16/B10, подрозетники, гофра, клипсы</t>
         </is>
       </c>
       <c r="K21" s="30" t="n"/>
       <c r="L21" s="30" t="n"/>
       <c r="M21" s="30" t="n"/>
       <c r="N21" s="30" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="57" t="n"/>
-      <c r="B22" s="57" t="n"/>
-      <c r="C22" s="57" t="n"/>
-      <c r="D22" s="65" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДОВ:</t>
-        </is>
-      </c>
-      <c r="E22" s="55">
-        <f>SUM(E5:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="55">
-        <f>SUM(F5:F21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="55">
-        <f>SUM(G5:G21)</f>
-        <v/>
-      </c>
-      <c r="H22" s="66">
+      <c r="O21" s="140" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="64" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="64" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="inlineStr">
+        <is>
+          <t>Двери и входная группа</t>
+        </is>
+      </c>
+      <c r="D22" s="49" t="inlineStr">
+        <is>
+          <t>Монтаж входной двери (демонтаж 2 старых дверей + установка новой)</t>
+        </is>
+      </c>
+      <c r="E22" s="50" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F22" s="51" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G22" s="47">
+        <f>E22-F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="63">
         <f>IFERROR(G22/E22, 0)</f>
         <v/>
       </c>
-      <c r="I22" s="57" t="n"/>
-      <c r="J22" s="57" t="n"/>
+      <c r="I22" s="49" t="inlineStr">
+        <is>
+          <t>Андрей (монтаж дверей)</t>
+        </is>
+      </c>
+      <c r="J22" s="49" t="inlineStr">
+        <is>
+          <t>Сняли 2 старые двери (деревянная + металл), установили новую</t>
+        </is>
+      </c>
       <c r="K22" s="30" t="n"/>
       <c r="L22" s="30" t="n"/>
       <c r="M22" s="30" t="n"/>
       <c r="N22" s="30" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="30" t="n"/>
-      <c r="B23" s="30" t="n"/>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="30" t="n"/>
-      <c r="H23" s="30" t="n"/>
-      <c r="I23" s="30" t="n"/>
-      <c r="J23" s="30" t="n"/>
+      <c r="O22" s="140" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="62" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="62" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="C23" s="44" t="inlineStr">
+        <is>
+          <t>Электрика / Материалы</t>
+        </is>
+      </c>
+      <c r="D23" s="44" t="inlineStr">
+        <is>
+          <t>Кабель силовой ВВГнг-LS (ГОСТ 3х2.5 и 3х1.5 для всех трасс)</t>
+        </is>
+      </c>
+      <c r="E23" s="45" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F23" s="46" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G23" s="47">
+        <f>E23-F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="63">
+        <f>IFERROR(G23/E23, 0)</f>
+        <v/>
+      </c>
+      <c r="I23" s="44" t="inlineStr">
+        <is>
+          <t>Электромонтаж / Поставщик</t>
+        </is>
+      </c>
+      <c r="J23" s="44" t="inlineStr">
+        <is>
+          <t>Силовой кабель ГОСТ для розеточных и осветительных групп</t>
+        </is>
+      </c>
       <c r="K23" s="30" t="n"/>
       <c r="L23" s="30" t="n"/>
       <c r="M23" s="30" t="n"/>
       <c r="N23" s="30" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="30" t="n"/>
-      <c r="B24" s="30" t="n"/>
-      <c r="C24" s="30" t="n"/>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="30" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="30" t="n"/>
-      <c r="I24" s="30" t="n"/>
-      <c r="J24" s="30" t="n"/>
+      <c r="O23" s="140" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="64" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="64" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>Электрика / Материалы</t>
+        </is>
+      </c>
+      <c r="D24" s="49" t="inlineStr">
+        <is>
+          <t>Стяжки нейлоновые и крепёж для монтажа кабеля</t>
+        </is>
+      </c>
+      <c r="E24" s="50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F24" s="51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G24" s="47">
+        <f>E24-F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="63">
+        <f>IFERROR(G24/E24, 0)</f>
+        <v/>
+      </c>
+      <c r="I24" s="49" t="inlineStr">
+        <is>
+          <t>Хозмаг / Электромонтаж</t>
+        </is>
+      </c>
+      <c r="J24" s="49" t="inlineStr">
+        <is>
+          <t>Расходники для фиксации кабельных трасс по потолку</t>
+        </is>
+      </c>
       <c r="K24" s="30" t="n"/>
       <c r="L24" s="30" t="n"/>
       <c r="M24" s="30" t="n"/>
       <c r="N24" s="30" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="n"/>
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="30" t="n"/>
-      <c r="G25" s="30" t="n"/>
-      <c r="H25" s="30" t="n"/>
-      <c r="I25" s="30" t="n"/>
-      <c r="J25" s="30" t="n"/>
+      <c r="O24" s="140" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="62" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="62" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="inlineStr">
+        <is>
+          <t>Электроэнергия / Учёт</t>
+        </is>
+      </c>
+      <c r="D25" s="44" t="inlineStr">
+        <is>
+          <t>Срочный выезд инспектора ТНС энерго Тула (снятие пломбы со старого счётчика за 5 дней)</t>
+        </is>
+      </c>
+      <c r="E25" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F25" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G25" s="47">
+        <f>E25-F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="63">
+        <f>IFERROR(G25/E25, 0)</f>
+        <v/>
+      </c>
+      <c r="I25" s="44" t="inlineStr">
+        <is>
+          <t>АО "ТНС энерго Тула"</t>
+        </is>
+      </c>
+      <c r="J25" s="44" t="inlineStr">
+        <is>
+          <t>ЦОК Каминского, ЛС 714199024362, услуга ускоренного выезда контролера (5 дней вместо 30)</t>
+        </is>
+      </c>
       <c r="K25" s="30" t="n"/>
       <c r="L25" s="30" t="n"/>
       <c r="M25" s="30" t="n"/>
       <c r="N25" s="30" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="30" t="n"/>
-      <c r="B26" s="30" t="n"/>
-      <c r="C26" s="30" t="n"/>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="30" t="n"/>
-      <c r="F26" s="30" t="n"/>
-      <c r="G26" s="30" t="n"/>
-      <c r="H26" s="30" t="n"/>
-      <c r="I26" s="30" t="n"/>
-      <c r="J26" s="30" t="n"/>
+      <c r="O25" s="140" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="64" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="64" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>Электрика / Работы</t>
+        </is>
+      </c>
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>Электромонтажные работы под ключ (разводка 32 точек, штробление, щит 18м, монтаж счётчика)</t>
+        </is>
+      </c>
+      <c r="E26" s="50" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F26" s="51" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G26" s="47">
+        <f>E26-F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="63">
+        <f>IFERROR(G26/E26, 0)</f>
+        <v/>
+      </c>
+      <c r="I26" s="49" t="inlineStr">
+        <is>
+          <t>Анатолий Кушнарев (бригада)</t>
+        </is>
+      </c>
+      <c r="J26" s="49" t="inlineStr">
+        <is>
+          <t>Монтаж проводки, сборка щита и подключение нового счётчика (рынок ~60к, экономия 10 000 ₽)</t>
+        </is>
+      </c>
       <c r="K26" s="30" t="n"/>
       <c r="L26" s="30" t="n"/>
       <c r="M26" s="30" t="n"/>
       <c r="N26" s="30" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="n"/>
-      <c r="B27" s="30" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="30" t="n"/>
-      <c r="G27" s="30" t="n"/>
-      <c r="H27" s="30" t="n"/>
-      <c r="I27" s="30" t="n"/>
-      <c r="J27" s="30" t="n"/>
+      <c r="O26" s="140" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="62" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="62" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="C27" s="44" t="inlineStr">
+        <is>
+          <t>Электрика / Материалы</t>
+        </is>
+      </c>
+      <c r="D27" s="44" t="inlineStr">
+        <is>
+          <t>Докупка силового кабеля ВВГнг-LS (дополнительный метраж трасс)</t>
+        </is>
+      </c>
+      <c r="E27" s="45" t="n">
+        <v>14500</v>
+      </c>
+      <c r="F27" s="46" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G27" s="47">
+        <f>E27-F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="63">
+        <f>IFERROR(G27/E27, 0)</f>
+        <v/>
+      </c>
+      <c r="I27" s="44" t="inlineStr">
+        <is>
+          <t>Электромонтаж / Поставщик</t>
+        </is>
+      </c>
+      <c r="J27" s="44" t="inlineStr">
+        <is>
+          <t>Дополнительный кабель ВВГнг-LS ГОСТ для трасс на кухню и бытовую технику (скидка 1 500 ₽)</t>
+        </is>
+      </c>
       <c r="K27" s="30" t="n"/>
       <c r="L27" s="30" t="n"/>
       <c r="M27" s="30" t="n"/>
       <c r="N27" s="30" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="30" t="n"/>
-      <c r="B28" s="30" t="n"/>
-      <c r="C28" s="30" t="n"/>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="30" t="n"/>
-      <c r="F28" s="30" t="n"/>
-      <c r="G28" s="30" t="n"/>
-      <c r="H28" s="30" t="n"/>
-      <c r="I28" s="30" t="n"/>
-      <c r="J28" s="30" t="n"/>
+      <c r="O27" s="140" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="64" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="64" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>Демонтаж и зачистка</t>
+        </is>
+      </c>
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>Зачистка стен/потолка (обои, плитка в зале и спальне), вынос мусора, 1-й слой грунта (спальня + гардеробная)</t>
+        </is>
+      </c>
+      <c r="E28" s="50" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F28" s="51" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G28" s="47">
+        <f>E28-F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="63">
+        <f>IFERROR(G28/E28, 0)</f>
+        <v/>
+      </c>
+      <c r="I28" s="49" t="inlineStr">
+        <is>
+          <t>Бригада разнорабочих</t>
+        </is>
+      </c>
+      <c r="J28" s="49" t="inlineStr">
+        <is>
+          <t>Снятие обоев, плитки с потолка, вынос люстр/плинтусов/мойки, грунтовка спальни и подсобки (скидка 5 000 ₽)</t>
+        </is>
+      </c>
       <c r="K28" s="30" t="n"/>
       <c r="L28" s="30" t="n"/>
       <c r="M28" s="30" t="n"/>
       <c r="N28" s="30" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="n"/>
-      <c r="B29" s="30" t="n"/>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="30" t="n"/>
-      <c r="H29" s="30" t="n"/>
-      <c r="I29" s="30" t="n"/>
-      <c r="J29" s="30" t="n"/>
+      <c r="O28" s="140" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="62" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="62" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="C29" s="44" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D29" s="44" t="inlineStr">
+        <is>
+          <t>Материалы для зачистки и грунтования, шпатлевка Старатели 20кг, грунт Axton 10л, антисептик СТ99, фильтр Rommer, расходники</t>
+        </is>
+      </c>
+      <c r="E29" s="45" t="n">
+        <v>4803.6</v>
+      </c>
+      <c r="F29" s="46" t="n">
+        <v>4803.6</v>
+      </c>
+      <c r="G29" s="47">
+        <f>E29-F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="63">
+        <f>IFERROR(G29/E29, 0)</f>
+        <v/>
+      </c>
+      <c r="I29" s="44" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J29" s="44" t="inlineStr">
+        <is>
+          <t>Чек от 30.08.2026 11:02: Шпатлевка 20кг (454₽), грунт 10л (460₽), CT99 (735₽), миксер (208₽), опрыскиватель (276₽), макловица, лента, тенты, подрозетник, щетки, фильтр Rommer 1/2 (341₽), уголок, шпатели, перчатки 10п, мешки, валики 2шт, кюветы 2шт</t>
+        </is>
+      </c>
       <c r="K29" s="30" t="n"/>
       <c r="L29" s="30" t="n"/>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="30" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="n"/>
-      <c r="B30" s="30" t="n"/>
-      <c r="C30" s="30" t="n"/>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="30" t="n"/>
-      <c r="F30" s="30" t="n"/>
-      <c r="G30" s="30" t="n"/>
-      <c r="H30" s="30" t="n"/>
-      <c r="I30" s="30" t="n"/>
-      <c r="J30" s="30" t="n"/>
+      <c r="O29" s="140" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="64" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="64" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="inlineStr">
+        <is>
+          <t>Инструмент и расходники</t>
+        </is>
+      </c>
+      <c r="D30" s="49" t="inlineStr">
+        <is>
+          <t>Ведро строительное 20 л (2 шт.)</t>
+        </is>
+      </c>
+      <c r="E30" s="50" t="n">
+        <v>256</v>
+      </c>
+      <c r="F30" s="51" t="n">
+        <v>256</v>
+      </c>
+      <c r="G30" s="47">
+        <f>E30-F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="63">
+        <f>IFERROR(G30/E30, 0)</f>
+        <v/>
+      </c>
+      <c r="I30" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J30" s="49" t="inlineStr">
+        <is>
+          <t>Чек от 30.08.2026 11:03: Ведра строительные 20л (2 шт. × 128 ₽)</t>
+        </is>
+      </c>
       <c r="K30" s="30" t="n"/>
       <c r="L30" s="30" t="n"/>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="30" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="30" t="n"/>
-      <c r="B31" s="30" t="n"/>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="30" t="n"/>
-      <c r="F31" s="30" t="n"/>
-      <c r="G31" s="30" t="n"/>
-      <c r="H31" s="30" t="n"/>
-      <c r="I31" s="30" t="n"/>
-      <c r="J31" s="30" t="n"/>
+      <c r="O30" s="140" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="62" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="62" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="C31" s="44" t="inlineStr">
+        <is>
+          <t>Хоз. инвентарь / Оснащение</t>
+        </is>
+      </c>
+      <c r="D31" s="44" t="inlineStr">
+        <is>
+          <t>Портативная акустика Xiaomi Bluetooth Speaker Essential Green (оснащение объекта)</t>
+        </is>
+      </c>
+      <c r="E31" s="45" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F31" s="46" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G31" s="47">
+        <f>E31-F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="63">
+        <f>IFERROR(G31/E31, 0)</f>
+        <v/>
+      </c>
+      <c r="I31" s="44" t="inlineStr">
+        <is>
+          <t>ООО ДНС Ритейл (DNS)</t>
+        </is>
+      </c>
+      <c r="J31" s="44" t="inlineStr">
+        <is>
+          <t>Чек от 30.08.2026 17:28: Колонка для комфортной работы бригады на объекте</t>
+        </is>
+      </c>
       <c r="K31" s="30" t="n"/>
       <c r="L31" s="30" t="n"/>
       <c r="M31" s="30" t="n"/>
       <c r="N31" s="30" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="30" t="n"/>
-      <c r="C32" s="30" t="n"/>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="30" t="n"/>
-      <c r="F32" s="30" t="n"/>
-      <c r="G32" s="30" t="n"/>
-      <c r="H32" s="30" t="n"/>
-      <c r="I32" s="30" t="n"/>
-      <c r="J32" s="30" t="n"/>
+      <c r="O31" s="140" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="94" t="n"/>
+      <c r="B32" s="94" t="n"/>
+      <c r="C32" s="54" t="n"/>
+      <c r="D32" s="65" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДОВ:</t>
+        </is>
+      </c>
+      <c r="E32" s="55">
+        <f>SUM(E5:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="55">
+        <f>SUM(F5:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="55">
+        <f>SUM(G5:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="104">
+        <f>IFERROR(G32/E32, 0)</f>
+        <v/>
+      </c>
+      <c r="I32" s="54" t="n"/>
+      <c r="J32" s="54" t="n"/>
       <c r="K32" s="30" t="n"/>
       <c r="L32" s="30" t="n"/>
       <c r="M32" s="30" t="n"/>
       <c r="N32" s="30" t="n"/>
+      <c r="O32" s="140" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="30" t="n"/>
@@ -2268,6 +3943,7 @@
       <c r="L33" s="30" t="n"/>
       <c r="M33" s="30" t="n"/>
       <c r="N33" s="30" t="n"/>
+      <c r="O33" s="140" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="30" t="n"/>
@@ -2284,6 +3960,7 @@
       <c r="L34" s="30" t="n"/>
       <c r="M34" s="30" t="n"/>
       <c r="N34" s="30" t="n"/>
+      <c r="O34" s="140" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="30" t="n"/>
@@ -2300,6 +3977,7 @@
       <c r="L35" s="30" t="n"/>
       <c r="M35" s="30" t="n"/>
       <c r="N35" s="30" t="n"/>
+      <c r="O35" s="140" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="30" t="n"/>
@@ -2445,6 +4123,118 @@
       <c r="M44" s="30" t="n"/>
       <c r="N44" s="30" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="140" t="n"/>
+      <c r="B45" s="140" t="n"/>
+      <c r="C45" s="140" t="n"/>
+      <c r="D45" s="140" t="n"/>
+      <c r="E45" s="140" t="n"/>
+      <c r="F45" s="140" t="n"/>
+      <c r="G45" s="140" t="n"/>
+      <c r="H45" s="140" t="n"/>
+      <c r="I45" s="140" t="n"/>
+      <c r="J45" s="140" t="n"/>
+      <c r="K45" s="140" t="n"/>
+      <c r="L45" s="140" t="n"/>
+      <c r="M45" s="140" t="n"/>
+      <c r="N45" s="140" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="140" t="n"/>
+      <c r="B46" s="140" t="n"/>
+      <c r="C46" s="140" t="n"/>
+      <c r="D46" s="140" t="n"/>
+      <c r="E46" s="140" t="n"/>
+      <c r="F46" s="140" t="n"/>
+      <c r="G46" s="140" t="n"/>
+      <c r="H46" s="140" t="n"/>
+      <c r="I46" s="140" t="n"/>
+      <c r="J46" s="140" t="n"/>
+      <c r="K46" s="140" t="n"/>
+      <c r="L46" s="140" t="n"/>
+      <c r="M46" s="140" t="n"/>
+      <c r="N46" s="140" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="140" t="n"/>
+      <c r="B47" s="140" t="n"/>
+      <c r="C47" s="140" t="n"/>
+      <c r="D47" s="140" t="n"/>
+      <c r="E47" s="140" t="n"/>
+      <c r="F47" s="140" t="n"/>
+      <c r="G47" s="140" t="n"/>
+      <c r="H47" s="140" t="n"/>
+      <c r="I47" s="140" t="n"/>
+      <c r="J47" s="140" t="n"/>
+      <c r="K47" s="140" t="n"/>
+      <c r="L47" s="140" t="n"/>
+      <c r="M47" s="140" t="n"/>
+      <c r="N47" s="140" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="140" t="n"/>
+      <c r="B48" s="140" t="n"/>
+      <c r="C48" s="140" t="n"/>
+      <c r="D48" s="140" t="n"/>
+      <c r="E48" s="140" t="n"/>
+      <c r="F48" s="140" t="n"/>
+      <c r="G48" s="140" t="n"/>
+      <c r="H48" s="140" t="n"/>
+      <c r="I48" s="140" t="n"/>
+      <c r="J48" s="140" t="n"/>
+      <c r="K48" s="140" t="n"/>
+      <c r="L48" s="140" t="n"/>
+      <c r="M48" s="140" t="n"/>
+      <c r="N48" s="140" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="140" t="n"/>
+      <c r="B49" s="140" t="n"/>
+      <c r="C49" s="140" t="n"/>
+      <c r="D49" s="140" t="n"/>
+      <c r="E49" s="140" t="n"/>
+      <c r="F49" s="140" t="n"/>
+      <c r="G49" s="140" t="n"/>
+      <c r="H49" s="140" t="n"/>
+      <c r="I49" s="140" t="n"/>
+      <c r="J49" s="140" t="n"/>
+      <c r="K49" s="140" t="n"/>
+      <c r="L49" s="140" t="n"/>
+      <c r="M49" s="140" t="n"/>
+      <c r="N49" s="140" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="140" t="n"/>
+      <c r="B50" s="140" t="n"/>
+      <c r="C50" s="140" t="n"/>
+      <c r="D50" s="140" t="n"/>
+      <c r="E50" s="140" t="n"/>
+      <c r="F50" s="140" t="n"/>
+      <c r="G50" s="140" t="n"/>
+      <c r="H50" s="140" t="n"/>
+      <c r="I50" s="140" t="n"/>
+      <c r="J50" s="140" t="n"/>
+      <c r="K50" s="140" t="n"/>
+      <c r="L50" s="140" t="n"/>
+      <c r="M50" s="140" t="n"/>
+      <c r="N50" s="140" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="140" t="n"/>
+      <c r="B51" s="140" t="n"/>
+      <c r="C51" s="140" t="n"/>
+      <c r="D51" s="140" t="n"/>
+      <c r="E51" s="140" t="n"/>
+      <c r="F51" s="140" t="n"/>
+      <c r="G51" s="140" t="n"/>
+      <c r="H51" s="140" t="n"/>
+      <c r="I51" s="140" t="n"/>
+      <c r="J51" s="140" t="n"/>
+      <c r="K51" s="140" t="n"/>
+      <c r="L51" s="140" t="n"/>
+      <c r="M51" s="140" t="n"/>
+      <c r="N51" s="140" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2457,26 +4247,26 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="38" t="inlineStr">
         <is>
           <t>СМЕТНЫЙ ПЛАН: РЫНОЧНАЯ СТОИМОСТЬ VS ЦЕЛЕВОЙ БЮДЖЕТ</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Сравнение среднерыночных цен Тулы с нашей целевой стоимостью выполнения</t>
@@ -2549,7 +4339,7 @@
         <f>D5-E5</f>
         <v/>
       </c>
-      <c r="G5" s="53" t="inlineStr">
+      <c r="G5" s="62" t="inlineStr">
         <is>
           <t>В работе</t>
         </is>
@@ -2584,7 +4374,7 @@
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="67" t="inlineStr">
+      <c r="G6" s="64" t="inlineStr">
         <is>
           <t>План</t>
         </is>
@@ -2619,7 +4409,7 @@
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="68" t="inlineStr">
+      <c r="G7" s="62" t="inlineStr">
         <is>
           <t>ТЗ готово</t>
         </is>
@@ -2654,7 +4444,7 @@
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="67" t="inlineStr">
+      <c r="G8" s="64" t="inlineStr">
         <is>
           <t>План</t>
         </is>
@@ -2689,7 +4479,7 @@
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="69" t="inlineStr">
+      <c r="G9" s="62" t="inlineStr">
         <is>
           <t>План</t>
         </is>
@@ -2724,7 +4514,7 @@
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="67" t="inlineStr">
+      <c r="G10" s="64" t="inlineStr">
         <is>
           <t>План</t>
         </is>
@@ -2759,7 +4549,7 @@
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="69" t="inlineStr">
+      <c r="G11" s="62" t="inlineStr">
         <is>
           <t>План</t>
         </is>
@@ -2794,7 +4584,7 @@
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="67" t="inlineStr">
+      <c r="G12" s="64" t="inlineStr">
         <is>
           <t>План</t>
         </is>
@@ -2829,7 +4619,7 @@
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="69" t="inlineStr">
+      <c r="G13" s="62" t="inlineStr">
         <is>
           <t>План</t>
         </is>
@@ -2864,7 +4654,7 @@
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="67" t="inlineStr">
+      <c r="G14" s="64" t="inlineStr">
         <is>
           <t>План</t>
         </is>
@@ -2899,7 +4689,7 @@
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="69" t="inlineStr">
+      <c r="G15" s="62" t="inlineStr">
         <is>
           <t>План</t>
         </is>
@@ -2911,13 +4701,13 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="57" t="n"/>
+      <c r="A16" s="94" t="n"/>
       <c r="B16" s="65" t="inlineStr">
         <is>
           <t>ИТОГО СМЕТА РЕМОНТА:</t>
         </is>
       </c>
-      <c r="C16" s="57" t="n"/>
+      <c r="C16" s="94" t="n"/>
       <c r="D16" s="55">
         <f>SUM(D5:D15)</f>
         <v/>
@@ -2926,12 +4716,12 @@
         <f>SUM(E5:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="56">
+      <c r="F16" s="55">
         <f>SUM(F5:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="57" t="n"/>
-      <c r="H16" s="57" t="n"/>
+      <c r="G16" s="54" t="n"/>
+      <c r="H16" s="54" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -535,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -955,6 +955,7 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1321,7 +1322,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -1389,7 +1390,7 @@
         <v/>
       </c>
       <c r="D5" s="118">
-        <f>'Факт расходов'!F32</f>
+        <f>'Факт расходов'!F36</f>
         <v/>
       </c>
       <c r="E5" s="118" t="n">
@@ -1488,7 +1489,7 @@
         <v>23000</v>
       </c>
       <c r="C11" s="46">
-        <f>SUMIF('Факт расходов'!C5:C31, "*Юр.*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*Безопасность*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*IT*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*Электроэнергия*", 'Факт расходов'!F5:F31)</f>
+        <f>SUMIF('Факт расходов'!C5:C35, "*Юр.*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*Безопасность*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*IT*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*Электроэнергия*", 'Факт расходов'!F5:F35)</f>
         <v/>
       </c>
       <c r="D11" s="124">
@@ -1774,7 +1775,7 @@
         <v/>
       </c>
       <c r="C23" s="46">
-        <f>SUMIF('Факт расходов'!C5:C31, "*Демонтаж*", 'Факт расходов'!F5:F31)</f>
+        <f>SUMIF('Факт расходов'!C5:C35, "*Демонтаж*", 'Факт расходов'!F5:F35)</f>
         <v/>
       </c>
       <c r="D23" s="45">
@@ -1807,7 +1808,7 @@
         <v/>
       </c>
       <c r="C24" s="51">
-        <f>SUMIF('Факт расходов'!C5:C31, "*Двери*", 'Факт расходов'!F5:F31)</f>
+        <f>SUMIF('Факт расходов'!C5:C35, "*Двери*", 'Факт расходов'!F5:F35)</f>
         <v/>
       </c>
       <c r="D24" s="50">
@@ -1840,7 +1841,7 @@
         <v/>
       </c>
       <c r="C25" s="46">
-        <f>SUMIF('Факт расходов'!C5:C31, "*Электрика*", 'Факт расходов'!F5:F31)</f>
+        <f>SUMIF('Факт расходов'!C5:C35, "*Электрика*", 'Факт расходов'!F5:F35)</f>
         <v/>
       </c>
       <c r="D25" s="45">
@@ -1873,7 +1874,7 @@
         <v/>
       </c>
       <c r="C26" s="51">
-        <f>SUMIF('Факт расходов'!C5:C31, "*Сантехника*", 'Факт расходов'!F5:F31)</f>
+        <f>SUMIF('Факт расходов'!C5:C35, "*Сантехника*", 'Факт расходов'!F5:F35)</f>
         <v/>
       </c>
       <c r="D26" s="50">
@@ -1905,7 +1906,7 @@
         <v>5000</v>
       </c>
       <c r="C27" s="46">
-        <f>SUMIF('Факт расходов'!C5:C31, "*Газ*", 'Факт расходов'!F5:F31)</f>
+        <f>SUMIF('Факт расходов'!C5:C35, "*Газ*", 'Факт расходов'!F5:F35)</f>
         <v/>
       </c>
       <c r="D27" s="45">
@@ -1970,7 +1971,7 @@
         <v/>
       </c>
       <c r="C29" s="46">
-        <f>SUMIF('Факт расходов'!C5:C31, "*Черновая*", 'Факт расходов'!F5:F31)</f>
+        <f>SUMIF('Факт расходов'!C5:C35, "*Черновая*", 'Факт расходов'!F5:F35)</f>
         <v/>
       </c>
       <c r="D29" s="45">
@@ -2162,7 +2163,7 @@
         <v>10000</v>
       </c>
       <c r="C35" s="46">
-        <f>SUMIF('Факт расходов'!C5:C31, "*Инструмент*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*Расходные*", 'Факт расходов'!F5:F31)</f>
+        <f>SUMIF('Факт расходов'!C5:C35, "*Инструмент*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*Расходные*", 'Факт расходов'!F5:F35)</f>
         <v/>
       </c>
       <c r="D35" s="45">
@@ -2194,7 +2195,7 @@
         <v>5000</v>
       </c>
       <c r="C36" s="51">
-        <f>SUMIF('Факт расходов'!C5:C31, "*хозмаг*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*Хоз.*", 'Факт расходов'!F5:F31)+SUMIF('Факт расходов'!C5:C31, "*Оснащение*", 'Факт расходов'!F5:F31)</f>
+        <f>SUMIF('Факт расходов'!C5:C35, "*хозмаг*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*Хоз.*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*Оснащение*", 'Факт расходов'!F5:F35)</f>
         <v/>
       </c>
       <c r="D36" s="50">
@@ -2382,11 +2383,11 @@
         </is>
       </c>
       <c r="B45" s="45">
-        <f>'Факт расходов'!E32</f>
+        <f>'Факт расходов'!E36</f>
         <v/>
       </c>
       <c r="C45" s="45">
-        <f>'Факт расходов'!F32</f>
+        <f>'Факт расходов'!F36</f>
         <v/>
       </c>
       <c r="D45" s="124">
@@ -2469,8 +2470,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:O55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -3895,101 +3896,229 @@
       <c r="N31" s="30" t="n"/>
       <c r="O31" s="140" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="94" t="n"/>
-      <c r="B32" s="94" t="n"/>
-      <c r="C32" s="54" t="n"/>
-      <c r="D32" s="65" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДОВ:</t>
-        </is>
-      </c>
-      <c r="E32" s="55">
-        <f>SUM(E5:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="55">
-        <f>SUM(F5:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="55">
-        <f>SUM(G5:G31)</f>
-        <v/>
-      </c>
-      <c r="H32" s="104">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="64" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="64" t="inlineStr">
+        <is>
+          <t>05.09.2026</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>Материалы для подготовки стен (грунт Axton 10л 4шт, шпатлевка Старатели 20кг 2шт, шпатели 150 и 350мм, мешки, дождевик)</t>
+        </is>
+      </c>
+      <c r="E32" s="50" t="n">
+        <v>3308</v>
+      </c>
+      <c r="F32" s="51" t="n">
+        <v>3308</v>
+      </c>
+      <c r="G32" s="47">
+        <f>E32-F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="63">
         <f>IFERROR(G32/E32, 0)</f>
         <v/>
       </c>
-      <c r="I32" s="54" t="n"/>
-      <c r="J32" s="54" t="n"/>
+      <c r="I32" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J32" s="49" t="inlineStr">
+        <is>
+          <t>Чек от 05.09.2026 10:23: Грунт Axton 10л (4шт по 460₽=1840₽), шпатлевка Старатели 20кг (2шт по 454₽=908₽), шпатель 150мм (87₽), шпатель 350мм (186₽), дождевик (248₽), мешки 3шт (39₽)</t>
+        </is>
+      </c>
       <c r="K32" s="30" t="n"/>
       <c r="L32" s="30" t="n"/>
       <c r="M32" s="30" t="n"/>
       <c r="N32" s="30" t="n"/>
       <c r="O32" s="140" t="n"/>
     </row>
-    <row r="33">
-      <c r="A33" s="30" t="n"/>
-      <c r="B33" s="30" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="30" t="n"/>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="30" t="n"/>
-      <c r="H33" s="30" t="n"/>
-      <c r="I33" s="30" t="n"/>
-      <c r="J33" s="30" t="n"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="62" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="62" t="inlineStr">
+        <is>
+          <t>05.09.2026</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="inlineStr">
+        <is>
+          <t>Хоз. инвентарь / Оснащение</t>
+        </is>
+      </c>
+      <c r="D33" s="44" t="inlineStr">
+        <is>
+          <t>Хозрасходы на объект: салфетки влажные и питьевая вода для мастеров</t>
+        </is>
+      </c>
+      <c r="E33" s="45" t="n">
+        <v>520</v>
+      </c>
+      <c r="F33" s="46" t="n">
+        <v>520</v>
+      </c>
+      <c r="G33" s="47">
+        <f>E33-F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="63">
+        <f>IFERROR(G33/E33, 0)</f>
+        <v/>
+      </c>
+      <c r="I33" s="44" t="inlineStr">
+        <is>
+          <t>Хозмаг / Продукты</t>
+        </is>
+      </c>
+      <c r="J33" s="44" t="inlineStr">
+        <is>
+          <t>Снабжение объекта для бригады: салфетки влажные, вода питьевая</t>
+        </is>
+      </c>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
       <c r="M33" s="30" t="n"/>
       <c r="N33" s="30" t="n"/>
       <c r="O33" s="140" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="30" t="n"/>
-      <c r="B34" s="30" t="n"/>
-      <c r="C34" s="30" t="n"/>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="30" t="n"/>
-      <c r="F34" s="30" t="n"/>
-      <c r="G34" s="30" t="n"/>
-      <c r="H34" s="30" t="n"/>
-      <c r="I34" s="30" t="n"/>
-      <c r="J34" s="30" t="n"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="64" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="64" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D34" s="49" t="inlineStr">
+        <is>
+          <t>Материалы для штукатурки и шпаклёвки (Бетонконтакт Axton 12кг 3шт, финиш Старатели 20кг 5шт, штукатурка Старатели 30кг 3шт, правило 1.5м, уголки, тент, расходники)</t>
+        </is>
+      </c>
+      <c r="E34" s="50" t="n">
+        <v>8162</v>
+      </c>
+      <c r="F34" s="51" t="n">
+        <v>8162</v>
+      </c>
+      <c r="G34" s="47">
+        <f>E34-F34</f>
+        <v/>
+      </c>
+      <c r="H34" s="63">
+        <f>IFERROR(G34/E34, 0)</f>
+        <v/>
+      </c>
+      <c r="I34" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J34" s="49" t="inlineStr">
+        <is>
+          <t>Чек от 06.09.2026 12:57: Бетонконтакт Axton 12кг (3шт по 903₽=2709₽), шпатлевка Старатели финиш 20кг (5шт по 530₽=2650₽), штукатурка Старатели 30кг (3шт по 505₽=1515₽), правило 1.5м (465₽), углы перф. 7шт (266₽), угол усил. 4шт (312₽), тент 4х12.5м (191₽), перчатки (54₽)</t>
+        </is>
+      </c>
       <c r="K34" s="30" t="n"/>
       <c r="L34" s="30" t="n"/>
       <c r="M34" s="30" t="n"/>
       <c r="N34" s="30" t="n"/>
       <c r="O34" s="140" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="30" t="n"/>
-      <c r="B35" s="30" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="30" t="n"/>
-      <c r="F35" s="30" t="n"/>
-      <c r="G35" s="30" t="n"/>
-      <c r="H35" s="30" t="n"/>
-      <c r="I35" s="30" t="n"/>
-      <c r="J35" s="30" t="n"/>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="62" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="62" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
+        </is>
+      </c>
+      <c r="C35" s="44" t="inlineStr">
+        <is>
+          <t>IT / AI-инфраструктура</t>
+        </is>
+      </c>
+      <c r="D35" s="44" t="inlineStr">
+        <is>
+          <t>Пополнение баланса OpenRouter (AI-ассистент Hermes)</t>
+        </is>
+      </c>
+      <c r="E35" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F35" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G35" s="47">
+        <f>E35-F35</f>
+        <v/>
+      </c>
+      <c r="H35" s="63">
+        <f>IFERROR(G35/E35, 0)</f>
+        <v/>
+      </c>
+      <c r="I35" s="44" t="inlineStr">
+        <is>
+          <t>OpenRouter</t>
+        </is>
+      </c>
+      <c r="J35" s="44" t="inlineStr">
+        <is>
+          <t>Пополнение баланса API для работы AI-партнёра Hermes (ведение проекта, аналитика, сметы)</t>
+        </is>
+      </c>
       <c r="K35" s="30" t="n"/>
       <c r="L35" s="30" t="n"/>
       <c r="M35" s="30" t="n"/>
       <c r="N35" s="30" t="n"/>
       <c r="O35" s="140" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" s="30" t="n"/>
-      <c r="B36" s="30" t="n"/>
-      <c r="C36" s="30" t="n"/>
-      <c r="D36" s="30" t="n"/>
-      <c r="E36" s="30" t="n"/>
-      <c r="F36" s="30" t="n"/>
-      <c r="G36" s="30" t="n"/>
-      <c r="H36" s="30" t="n"/>
-      <c r="I36" s="30" t="n"/>
-      <c r="J36" s="30" t="n"/>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="94" t="n"/>
+      <c r="B36" s="94" t="n"/>
+      <c r="C36" s="54" t="n"/>
+      <c r="D36" s="65" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДОВ:</t>
+        </is>
+      </c>
+      <c r="E36" s="55">
+        <f>SUM(E5:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="55">
+        <f>SUM(F5:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="55">
+        <f>SUM(G5:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="104">
+        <f>IFERROR(G36/E36, 0)</f>
+        <v/>
+      </c>
+      <c r="I36" s="54" t="n"/>
+      <c r="J36" s="54" t="n"/>
       <c r="K36" s="30" t="n"/>
       <c r="L36" s="30" t="n"/>
       <c r="M36" s="30" t="n"/>
@@ -4235,6 +4364,70 @@
       <c r="M51" s="140" t="n"/>
       <c r="N51" s="140" t="n"/>
     </row>
+    <row r="52">
+      <c r="A52" s="140" t="n"/>
+      <c r="B52" s="140" t="n"/>
+      <c r="C52" s="140" t="n"/>
+      <c r="D52" s="140" t="n"/>
+      <c r="E52" s="140" t="n"/>
+      <c r="F52" s="140" t="n"/>
+      <c r="G52" s="140" t="n"/>
+      <c r="H52" s="140" t="n"/>
+      <c r="I52" s="140" t="n"/>
+      <c r="J52" s="140" t="n"/>
+      <c r="K52" s="140" t="n"/>
+      <c r="L52" s="140" t="n"/>
+      <c r="M52" s="140" t="n"/>
+      <c r="N52" s="140" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="140" t="n"/>
+      <c r="B53" s="140" t="n"/>
+      <c r="C53" s="140" t="n"/>
+      <c r="D53" s="140" t="n"/>
+      <c r="E53" s="140" t="n"/>
+      <c r="F53" s="140" t="n"/>
+      <c r="G53" s="140" t="n"/>
+      <c r="H53" s="140" t="n"/>
+      <c r="I53" s="140" t="n"/>
+      <c r="J53" s="140" t="n"/>
+      <c r="K53" s="140" t="n"/>
+      <c r="L53" s="140" t="n"/>
+      <c r="M53" s="140" t="n"/>
+      <c r="N53" s="140" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="140" t="n"/>
+      <c r="B54" s="140" t="n"/>
+      <c r="C54" s="140" t="n"/>
+      <c r="D54" s="140" t="n"/>
+      <c r="E54" s="140" t="n"/>
+      <c r="F54" s="140" t="n"/>
+      <c r="G54" s="140" t="n"/>
+      <c r="H54" s="140" t="n"/>
+      <c r="I54" s="140" t="n"/>
+      <c r="J54" s="140" t="n"/>
+      <c r="K54" s="140" t="n"/>
+      <c r="L54" s="140" t="n"/>
+      <c r="M54" s="140" t="n"/>
+      <c r="N54" s="140" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="140" t="n"/>
+      <c r="B55" s="140" t="n"/>
+      <c r="C55" s="140" t="n"/>
+      <c r="D55" s="140" t="n"/>
+      <c r="E55" s="140" t="n"/>
+      <c r="F55" s="140" t="n"/>
+      <c r="G55" s="140" t="n"/>
+      <c r="H55" s="140" t="n"/>
+      <c r="I55" s="140" t="n"/>
+      <c r="J55" s="140" t="n"/>
+      <c r="K55" s="140" t="n"/>
+      <c r="L55" s="140" t="n"/>
+      <c r="M55" s="140" t="n"/>
+      <c r="N55" s="140" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4247,7 +4440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>

--- a/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
+++ b/profile/obsidian/Недвижимость/Фрунзе 17/Смета_и_чеки/Фрунзе17_Бюджет_и_Факт_расходов.xlsx
@@ -1390,7 +1390,7 @@
         <v/>
       </c>
       <c r="D5" s="118">
-        <f>'Факт расходов'!F36</f>
+        <f>'Факт расходов'!F38</f>
         <v/>
       </c>
       <c r="E5" s="118" t="n">
@@ -1489,7 +1489,7 @@
         <v>23000</v>
       </c>
       <c r="C11" s="46">
-        <f>SUMIF('Факт расходов'!C5:C35, "*Юр.*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*Безопасность*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*IT*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*Электроэнергия*", 'Факт расходов'!F5:F35)</f>
+        <f>SUMIF('Факт расходов'!C5:C37, "*Юр.*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*Безопасность*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*IT*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*Электроэнергия*", 'Факт расходов'!F5:F37)</f>
         <v/>
       </c>
       <c r="D11" s="124">
@@ -1775,7 +1775,7 @@
         <v/>
       </c>
       <c r="C23" s="46">
-        <f>SUMIF('Факт расходов'!C5:C35, "*Демонтаж*", 'Факт расходов'!F5:F35)</f>
+        <f>SUMIF('Факт расходов'!C5:C37, "*Демонтаж*", 'Факт расходов'!F5:F37)</f>
         <v/>
       </c>
       <c r="D23" s="45">
@@ -1808,7 +1808,7 @@
         <v/>
       </c>
       <c r="C24" s="51">
-        <f>SUMIF('Факт расходов'!C5:C35, "*Двери*", 'Факт расходов'!F5:F35)</f>
+        <f>SUMIF('Факт расходов'!C5:C37, "*Двери*", 'Факт расходов'!F5:F37)</f>
         <v/>
       </c>
       <c r="D24" s="50">
@@ -1841,7 +1841,7 @@
         <v/>
       </c>
       <c r="C25" s="46">
-        <f>SUMIF('Факт расходов'!C5:C35, "*Электрика*", 'Факт расходов'!F5:F35)</f>
+        <f>SUMIF('Факт расходов'!C5:C37, "*Электрика*", 'Факт расходов'!F5:F37)</f>
         <v/>
       </c>
       <c r="D25" s="45">
@@ -1874,7 +1874,7 @@
         <v/>
       </c>
       <c r="C26" s="51">
-        <f>SUMIF('Факт расходов'!C5:C35, "*Сантехника*", 'Факт расходов'!F5:F35)</f>
+        <f>SUMIF('Факт расходов'!C5:C37, "*Сантехника*", 'Факт расходов'!F5:F37)</f>
         <v/>
       </c>
       <c r="D26" s="50">
@@ -1906,7 +1906,7 @@
         <v>5000</v>
       </c>
       <c r="C27" s="46">
-        <f>SUMIF('Факт расходов'!C5:C35, "*Газ*", 'Факт расходов'!F5:F35)</f>
+        <f>SUMIF('Факт расходов'!C5:C37, "*Газ*", 'Факт расходов'!F5:F37)</f>
         <v/>
       </c>
       <c r="D27" s="45">
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="C29" s="46">
-        <f>SUMIF('Факт расходов'!C5:C35, "*Черновая*", 'Факт расходов'!F5:F35)</f>
+        <f>SUMIF('Факт расходов'!C5:C37, "*Черновая*", 'Факт расходов'!F5:F37)</f>
         <v/>
       </c>
       <c r="D29" s="45">
@@ -2163,7 +2163,7 @@
         <v>10000</v>
       </c>
       <c r="C35" s="46">
-        <f>SUMIF('Факт расходов'!C5:C35, "*Инструмент*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*Расходные*", 'Факт расходов'!F5:F35)</f>
+        <f>SUMIF('Факт расходов'!C5:C37, "*Инструмент*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*Расходные*", 'Факт расходов'!F5:F37)</f>
         <v/>
       </c>
       <c r="D35" s="45">
@@ -2195,7 +2195,7 @@
         <v>5000</v>
       </c>
       <c r="C36" s="51">
-        <f>SUMIF('Факт расходов'!C5:C35, "*хозмаг*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*Хоз.*", 'Факт расходов'!F5:F35)+SUMIF('Факт расходов'!C5:C35, "*Оснащение*", 'Факт расходов'!F5:F35)</f>
+        <f>SUMIF('Факт расходов'!C5:C37, "*хозмаг*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*Хоз.*", 'Факт расходов'!F5:F37)+SUMIF('Факт расходов'!C5:C37, "*Оснащение*", 'Факт расходов'!F5:F37)</f>
         <v/>
       </c>
       <c r="D36" s="50">
@@ -2383,11 +2383,11 @@
         </is>
       </c>
       <c r="B45" s="45">
-        <f>'Факт расходов'!E36</f>
+        <f>'Факт расходов'!E38</f>
         <v/>
       </c>
       <c r="C45" s="45">
-        <f>'Факт расходов'!F36</f>
+        <f>'Факт расходов'!F38</f>
         <v/>
       </c>
       <c r="D45" s="124">
@@ -2470,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4092,65 +4092,129 @@
       <c r="N35" s="30" t="n"/>
       <c r="O35" s="140" t="n"/>
     </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="94" t="n"/>
-      <c r="B36" s="94" t="n"/>
-      <c r="C36" s="54" t="n"/>
-      <c r="D36" s="65" t="inlineStr">
-        <is>
-          <t>ИТОГО РАСХОДОВ:</t>
-        </is>
-      </c>
-      <c r="E36" s="55">
-        <f>SUM(E5:E35)</f>
-        <v/>
-      </c>
-      <c r="F36" s="55">
-        <f>SUM(F5:F35)</f>
-        <v/>
-      </c>
-      <c r="G36" s="55">
-        <f>SUM(G5:G35)</f>
-        <v/>
-      </c>
-      <c r="H36" s="104">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="64" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="64" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="inlineStr">
+        <is>
+          <t>Черновая отделка / Материалы</t>
+        </is>
+      </c>
+      <c r="D36" s="49" t="inlineStr">
+        <is>
+          <t>Материалы для штукатурки и шпаклёвки (шпатлевка Старатели финиш 20кг, штукатурка Старатели 30кг 2шт, перчатки)</t>
+        </is>
+      </c>
+      <c r="E36" s="50" t="n">
+        <v>1594</v>
+      </c>
+      <c r="F36" s="51" t="n">
+        <v>1594</v>
+      </c>
+      <c r="G36" s="47">
+        <f>E36-F36</f>
+        <v/>
+      </c>
+      <c r="H36" s="63">
         <f>IFERROR(G36/E36, 0)</f>
         <v/>
       </c>
-      <c r="I36" s="54" t="n"/>
-      <c r="J36" s="54" t="n"/>
+      <c r="I36" s="49" t="inlineStr">
+        <is>
+          <t>ООО Ле Монлид (Лемана ПРО)</t>
+        </is>
+      </c>
+      <c r="J36" s="49" t="inlineStr">
+        <is>
+          <t>Чек от 08.09.2026 08:44: Шпатлевка Старатели финиш 20кг (530₽), штукатурка Старатели 30кг (2шт по 505₽=1010₽), перчатки 2п (54₽)</t>
+        </is>
+      </c>
       <c r="K36" s="30" t="n"/>
       <c r="L36" s="30" t="n"/>
       <c r="M36" s="30" t="n"/>
       <c r="N36" s="30" t="n"/>
     </row>
-    <row r="37">
-      <c r="A37" s="30" t="n"/>
-      <c r="B37" s="30" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="30" t="n"/>
-      <c r="F37" s="30" t="n"/>
-      <c r="G37" s="30" t="n"/>
-      <c r="H37" s="30" t="n"/>
-      <c r="I37" s="30" t="n"/>
-      <c r="J37" s="30" t="n"/>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="62" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="62" t="inlineStr">
+        <is>
+          <t>08.09.2026</t>
+        </is>
+      </c>
+      <c r="C37" s="44" t="inlineStr">
+        <is>
+          <t>Электроэнергия / Учёт</t>
+        </is>
+      </c>
+      <c r="D37" s="44" t="inlineStr">
+        <is>
+          <t>Дистанционная распломбировка старого электросчётчика (официальная услуга/согласование)</t>
+        </is>
+      </c>
+      <c r="E37" s="45" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F37" s="46" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G37" s="47">
+        <f>E37-F37</f>
+        <v/>
+      </c>
+      <c r="H37" s="63">
+        <f>IFERROR(G37/E37, 0)</f>
+        <v/>
+      </c>
+      <c r="I37" s="44" t="inlineStr">
+        <is>
+          <t>ТНС энерго Тула / Энергосбыт</t>
+        </is>
+      </c>
+      <c r="J37" s="44" t="inlineStr">
+        <is>
+          <t>Оплата услуги дистанционной распломбировки старого прибора учёта (фиксация контрольных показаний и снятие пломбы без выезда)</t>
+        </is>
+      </c>
       <c r="K37" s="30" t="n"/>
       <c r="L37" s="30" t="n"/>
       <c r="M37" s="30" t="n"/>
       <c r="N37" s="30" t="n"/>
     </row>
-    <row r="38">
-      <c r="A38" s="30" t="n"/>
-      <c r="B38" s="30" t="n"/>
-      <c r="C38" s="30" t="n"/>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="30" t="n"/>
-      <c r="F38" s="30" t="n"/>
-      <c r="G38" s="30" t="n"/>
-      <c r="H38" s="30" t="n"/>
-      <c r="I38" s="30" t="n"/>
-      <c r="J38" s="30" t="n"/>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="94" t="n"/>
+      <c r="B38" s="94" t="n"/>
+      <c r="C38" s="54" t="n"/>
+      <c r="D38" s="65" t="inlineStr">
+        <is>
+          <t>ИТОГО РАСХОДОВ:</t>
+        </is>
+      </c>
+      <c r="E38" s="55">
+        <f>SUM(E5:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="55">
+        <f>SUM(F5:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="55">
+        <f>SUM(G5:G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="104">
+        <f>IFERROR(G38/E38, 0)</f>
+        <v/>
+      </c>
+      <c r="I38" s="54" t="n"/>
+      <c r="J38" s="54" t="n"/>
       <c r="K38" s="30" t="n"/>
       <c r="L38" s="30" t="n"/>
       <c r="M38" s="30" t="n"/>
@@ -4427,6 +4491,38 @@
       <c r="L55" s="140" t="n"/>
       <c r="M55" s="140" t="n"/>
       <c r="N55" s="140" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="140" t="n"/>
+      <c r="B56" s="140" t="n"/>
+      <c r="C56" s="140" t="n"/>
+      <c r="D56" s="140" t="n"/>
+      <c r="E56" s="140" t="n"/>
+      <c r="F56" s="140" t="n"/>
+      <c r="G56" s="140" t="n"/>
+      <c r="H56" s="140" t="n"/>
+      <c r="I56" s="140" t="n"/>
+      <c r="J56" s="140" t="n"/>
+      <c r="K56" s="140" t="n"/>
+      <c r="L56" s="140" t="n"/>
+      <c r="M56" s="140" t="n"/>
+      <c r="N56" s="140" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="140" t="n"/>
+      <c r="B57" s="140" t="n"/>
+      <c r="C57" s="140" t="n"/>
+      <c r="D57" s="140" t="n"/>
+      <c r="E57" s="140" t="n"/>
+      <c r="F57" s="140" t="n"/>
+      <c r="G57" s="140" t="n"/>
+      <c r="H57" s="140" t="n"/>
+      <c r="I57" s="140" t="n"/>
+      <c r="J57" s="140" t="n"/>
+      <c r="K57" s="140" t="n"/>
+      <c r="L57" s="140" t="n"/>
+      <c r="M57" s="140" t="n"/>
+      <c r="N57" s="140" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
